--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -729,31 +729,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>DNW</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>VCO Munster W vs Ostbevern W</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Ostbevern W</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -761,16 +761,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>65.59999999999999</v>
+        <v>62.1</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -797,31 +797,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>PT2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Santo Andre vs Maia</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -829,31 +829,31 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>64.3</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
@@ -865,31 +865,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Odense W vs Gyor W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Gyor W</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>71.7</v>
+        <v>64.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -906,17 +906,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -943,21 +943,21 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>LNB</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Cholet vs Chalon/Saone</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Cholet</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -965,31 +965,31 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>70.5</v>
+        <v>71.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1001,68 +1001,136 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>20:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>basketball</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>FR2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>Ada Blois vs La Rochelle</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Ada Blois</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>1.38</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>77.59999999999999</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2-0</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>81%</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1073,7 +1141,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1512,7 +1580,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1522,21 +1590,21 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>DNW</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>VCO Munster W vs Ostbevern W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Ostbevern W</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1544,26 +1612,26 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>65.5</v>
+        <v>62.1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1580,31 +1648,31 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Bydgoszcz W</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1612,7 +1680,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>66.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -1621,17 +1689,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1648,68 +1716,136 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="D10" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="G10" t="n">
         <v>2</v>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I9" t="n">
+      <c r="I10" t="n">
         <v>56.3</v>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="N10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -520,36 +520,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>04:35</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>J1 League</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>JEF United Chiba vs Yokohama Marinos</t>
+          <t>Canterbury vs Taranaki</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Yokohama Marinos</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.43</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>56.3</v>
+        <v>72.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -566,17 +566,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -588,36 +588,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AUW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>C. Burel vs L. Romero Gormaz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>C. Burel</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -625,135 +620,135 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>66.09999999999999</v>
+        <v>74.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.53</v>
+        <v>1.63</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>65.5</v>
+        <v>75.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DNW</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -761,26 +756,26 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>62.1</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -792,36 +787,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -829,67 +824,67 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>65.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Engelholm W vs Linkopings W</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Engelholm W</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -897,7 +892,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>64.3</v>
+        <v>72.7</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -906,17 +901,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -928,36 +923,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -965,7 +960,7 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>71.7</v>
+        <v>65.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -974,17 +969,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -993,144 +988,8 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PT2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Academica vs CB Queluz</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>CB Queluz</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-17</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Ada Blois vs La Rochelle</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Ada Blois</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>77.59999999999999</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1141,7 +1000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1235,36 +1094,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.38</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1272,7 +1131,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>77.59999999999999</v>
+        <v>65.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1281,17 +1140,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1303,36 +1162,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Engelholm W vs Linkopings W</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Engelholm W</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1340,67 +1199,67 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>70.5</v>
+        <v>72.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1408,7 +1267,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>71.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1417,17 +1276,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1439,12 +1298,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1454,21 +1313,21 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1476,135 +1335,130 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>64.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>65.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DNW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>C. Burel vs L. Romero Gormaz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>C. Burel</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1612,67 +1466,67 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>62.1</v>
+        <v>74.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>04:35</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>Canterbury vs Taranaki</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1680,31 +1534,31 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>65.5</v>
+        <v>72.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1570,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1726,21 +1580,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Ada Blois vs La Rochelle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Ada Blois</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1748,31 +1602,31 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>66.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1784,68 +1638,544 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="G17" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I10" t="n">
+      <c r="I17" t="n">
         <v>56.3</v>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$18</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -792,31 +792,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>Ritten vs Asiago</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>Ritten</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -824,26 +824,26 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>68.09999999999999</v>
+        <v>67.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -865,26 +865,26 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.6</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>72.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -901,17 +901,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -928,68 +928,136 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>SEW</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Engelholm W vs Linkopings W</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Engelholm W</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>hockey</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>CEX</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>Karlovy Vary</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>2.1</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="n">
+      <c r="I9" t="n">
         <v>65.3</v>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J9" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>3-2</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>84%</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1000,7 +1068,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:N18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1303,31 +1371,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DE1</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>Ritten vs Asiago</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>Ritten</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1335,16 +1403,16 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>68.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1354,12 +1422,12 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1371,63 +1439,63 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ERC</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>75.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1439,53 +1507,58 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1502,31 +1575,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>C. Burel vs L. Romero Gormaz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>C. Burel</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1534,16 +1602,16 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>72.8</v>
+        <v>74.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1553,7 +1621,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1565,36 +1633,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Canterbury vs Taranaki</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1602,7 +1670,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>77.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1611,17 +1679,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1638,7 +1706,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1648,21 +1716,21 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Ada Blois vs La Rochelle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Ada Blois</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1670,31 +1738,31 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>70.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1716,21 +1784,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>PT2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Academica vs CB Queluz</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>CB Queluz</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1738,31 +1806,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1774,31 +1842,31 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>LNB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Cholet vs Chalon/Saone</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Cholet</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1806,7 +1874,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -1815,17 +1883,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1842,31 +1910,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Odense W vs Gyor W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Gyor W</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1874,31 +1942,31 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1910,31 +1978,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>DNW</t>
+          <t>PT2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>Santo Andre vs Maia</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1942,16 +2010,16 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>62.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1961,7 +2029,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1978,7 +2046,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1988,21 +2056,21 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>DNW</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>VCO Munster W vs Ostbevern W</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Ostbevern W</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2010,26 +2078,26 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>65.5</v>
+        <v>62.1</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2046,31 +2114,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Bydgoszcz W</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2078,7 +2146,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>66.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2087,17 +2155,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2114,68 +2182,136 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="G18" t="n">
         <v>2</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I17" t="n">
+      <c r="I18" t="n">
         <v>56.3</v>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N17"/>
+  <autoFilter ref="A1:N18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$19</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N9"/>
+  <dimension ref="A1:N10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1056,8 +1056,76 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>1. Liga</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N9"/>
+  <autoFilter ref="A1:N10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1068,7 +1136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1167,39 +1235,39 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>1. Liga</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>65.3</v>
+        <v>68.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1208,17 +1276,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1235,31 +1303,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.48</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1267,7 +1335,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>72.7</v>
+        <v>65.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1276,17 +1344,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1308,26 +1376,26 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>Engelholm W vs Linkopings W</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>Engelholm W</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1335,7 +1403,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>68.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1344,17 +1412,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1371,31 +1439,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1403,26 +1471,26 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>67.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -1439,31 +1507,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>DE1</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>Ritten vs Asiago</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>Ritten</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1471,16 +1539,16 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>68.90000000000001</v>
+        <v>67.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1490,12 +1558,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1507,63 +1575,63 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>ERC</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>75.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1575,53 +1643,58 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>74.5</v>
+        <v>75.3</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1638,31 +1711,26 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>C. Burel vs L. Romero Gormaz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>C. Burel</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1670,16 +1738,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>72.8</v>
+        <v>74.5</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1689,7 +1757,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1701,36 +1769,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Canterbury vs Taranaki</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1738,7 +1806,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>77.59999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1747,17 +1815,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1774,7 +1842,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1784,21 +1852,21 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Ada Blois vs La Rochelle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Ada Blois</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1806,31 +1874,31 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>70.5</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1852,21 +1920,21 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>PT2</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Academica vs CB Queluz</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>CB Queluz</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1874,31 +1942,31 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>71.7</v>
+        <v>70.5</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
@@ -1910,31 +1978,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>LNB</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Cholet vs Chalon/Saone</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Cholet</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.45</v>
+        <v>1.68</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1942,7 +2010,7 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>64.3</v>
+        <v>71.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -1951,17 +2019,17 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1978,31 +2046,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>CLW</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Odense W vs Gyor W</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Gyor W</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2010,31 +2078,31 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>65.59999999999999</v>
+        <v>64.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -2046,31 +2114,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>DNW</t>
+          <t>PT2</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>Santo Andre vs Maia</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>Maia</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2078,16 +2146,16 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>62.1</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2097,7 +2165,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2114,7 +2182,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2124,21 +2192,21 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>DNW</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>VCO Munster W vs Ostbevern W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Ostbevern W</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2146,26 +2214,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>65.5</v>
+        <v>62.1</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2182,31 +2250,31 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Bydgoszcz W</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>1.53</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2214,7 +2282,7 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>66.09999999999999</v>
+        <v>65.5</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
@@ -2223,17 +2291,17 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2250,68 +2318,136 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="G19" t="n">
         <v>2</v>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>56.3</v>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N18"/>
+  <autoFilter ref="A1:N19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$10</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N10"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -520,36 +520,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>B. Van De Zandschulp</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -557,26 +552,26 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>72.8</v>
+        <v>62.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -588,12 +583,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -603,43 +598,43 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>M. Cilic vs N. Basilashvili</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>N. Basilashvili</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>1.662</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>74.5</v>
+        <v>70.3</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -651,32 +646,32 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ERC</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>Nagasaki vs Altiri Chiba</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -684,71 +679,71 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>75.3</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>DE1</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>Utsunomiya Brex vs Gunma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>Gunma</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -756,7 +751,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>68.90000000000001</v>
+        <v>59.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -765,17 +760,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -787,12 +782,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -802,21 +797,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>KZ1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>Karaganda vs Gornyak Rudny</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>Karaganda</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1.65</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -824,7 +819,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>67.5</v>
+        <v>66.8</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -833,12 +828,12 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -855,36 +850,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ECU</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>A. Hernandez vs F. Ribero</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>A. Hernandez</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -892,16 +882,16 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>68.09999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -911,7 +901,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -923,36 +913,36 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>Primera C Metropolitana</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>CA Lugano vs Cañuelas FC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Cañuelas FC</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.48</v>
+        <v>2.15</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -960,172 +950,36 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>72.7</v>
+        <v>55.7</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CEX</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Litvinov vs Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Karlovy Vary</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>84%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-18</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>22:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>1. Liga</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Lechia Gdansk</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>68.3</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>4-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N10"/>
+  <autoFilter ref="A1:N8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1136,7 +990,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1230,12 +1084,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1245,17 +1099,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1. Liga</t>
+          <t>Primera C Metropolitana</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
+          <t>CA Lugano vs Cañuelas FC</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Cañuelas FC</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1263,71 +1117,66 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>68.3</v>
+        <v>55.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CEX</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>A. Hernandez vs F. Ribero</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>A. Hernandez</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1335,26 +1184,26 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>65.3</v>
+        <v>72.5</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1366,36 +1215,36 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>KZ1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>Karaganda vs Gornyak Rudny</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Karaganda</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1403,26 +1252,26 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>72.7</v>
+        <v>66.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1434,36 +1283,36 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>Utsunomiya Brex vs Gunma</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>Gunma</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -1471,67 +1320,67 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>68.09999999999999</v>
+        <v>59.3</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>Nagasaki vs Altiri Chiba</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.88</v>
+        <v>1.63</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1539,162 +1388,152 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>67.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>DE1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>M. Cilic vs N. Basilashvili</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>N. Basilashvili</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.7</v>
+        <v>1.662</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>68.90000000000001</v>
+        <v>70.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ERC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>B. Van De Zandschulp</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>75.3</v>
+        <v>62.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1711,53 +1550,58 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1. Liga</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.35</v>
+        <v>2.15</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>74.5</v>
+        <v>68.3</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1774,31 +1618,31 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1806,7 +1650,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>72.8</v>
+        <v>65.3</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1815,17 +1659,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1837,36 +1681,36 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Engelholm W vs Linkopings W</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Engelholm W</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1874,7 +1718,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>77.59999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1883,17 +1727,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1905,36 +1749,36 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1942,67 +1786,67 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>70.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Ritten vs Asiago</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Ritten</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.68</v>
+        <v>1.88</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2010,16 +1854,16 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>71.7</v>
+        <v>67.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2029,7 +1873,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -2041,12 +1885,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2056,21 +1900,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.45</v>
+        <v>1.7</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2078,135 +1922,130 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>64.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>65.59999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>DNW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>C. Burel vs L. Romero Gormaz</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>C. Burel</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2214,67 +2053,67 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>62.1</v>
+        <v>74.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>04:35</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>NPC</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>Canterbury vs Taranaki</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Canterbury</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2282,31 +2121,31 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>65.5</v>
+        <v>72.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -2318,7 +2157,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2328,21 +2167,21 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Ada Blois vs La Rochelle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Ada Blois</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
@@ -2350,31 +2189,31 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>66.09999999999999</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -2386,68 +2225,544 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D26" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="G26" t="n">
         <v>2</v>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I26" t="n">
         <v>56.3</v>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N19"/>
+  <autoFilter ref="A1:N26"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$8</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -520,58 +520,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+          <t>Washington Capitals vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.55</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>62.8</v>
+        <v>74.5</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -583,75 +588,80 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>M. Cilic vs N. Basilashvili</t>
+          <t>New York Islanders vs Anaheim Ducks</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>N. Basilashvili</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.662</v>
+        <v>2.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>70.3</v>
+        <v>57.4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -661,89 +671,84 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>LBP</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Nagasaki vs Altiri Chiba</t>
+          <t>Astros vs Mineros</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>Astros</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>64.09999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>BLJ</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Gunma</t>
+          <t>T. Valentova vs S. Zhang</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gunma</t>
+          <t>T. Valentova</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -751,67 +756,62 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>59.3</v>
+        <v>75.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>KZ1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Karaganda vs Gornyak Rudny</t>
+          <t>S. Kartal vs K. Birrell</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Karaganda</t>
+          <t>S. Kartal</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>66.8</v>
+        <v>70.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -828,17 +828,17 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -850,12 +850,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -865,12 +865,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>A. Hernandez vs F. Ribero</t>
+          <t>R. M. Papoe vs O. Roca Batalla</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>A. Hernandez</t>
+          <t>R. M. Papoe</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>72.5</v>
+        <v>76.2</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -891,17 +891,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -913,73 +913,869 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>M. Donald vs C. Sanchez Jover</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>M. Donald</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>83</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CBA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Beijing vs Guangdong</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Beijing</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>S. Kopp vs G. Cadenasso</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>G. Cadenasso</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>84.2</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0-0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>J. Fearnley vs H. Gaston</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>J. Fearnley</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Primera C Metropolitana</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>CA Lugano vs Cañuelas FC</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Cañuelas FC</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>League 1</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ario Eslamshahr</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>FI1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>SaiPa vs Karpat</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>SaiPa</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Karlovy Vary vs Kometa Brno</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>T. Samuel vs Z. Bergs</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Z. Bergs</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>63.3</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Liga 2</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Chindia Targoviste</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>K. Miyoshi vs M. Cassone</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>M. Cassone</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>76.09999999999999</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Hyeres-Toulon vs Le Havre</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Hyeres-Toulon</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>FR1</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Tours vs Tourcoing</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tours</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>75.7</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>22:45</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>League One</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Notts County vs Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Sheffield Wednesday</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
         <v>2.15</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I8" t="n">
-        <v>55.7</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>2-2</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
+      <c r="I20" t="n">
+        <v>60.4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N8"/>
+  <autoFilter ref="A1:N20"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -990,7 +1786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1084,12 +1880,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1099,17 +1895,17 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Primera C Metropolitana</t>
+          <t>League One</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CA Lugano vs Cañuelas FC</t>
+          <t>Notts County vs Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cañuelas FC</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1121,62 +1917,67 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>55.7</v>
+        <v>60.4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
+          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FR1</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>A. Hernandez vs F. Ribero</t>
+          <t>Tours vs Tourcoing</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>A. Hernandez</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1184,26 +1985,26 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>72.5</v>
+        <v>75.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1215,63 +2016,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KZ1</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Karaganda vs Gornyak Rudny</t>
+          <t>Hyeres-Toulon vs Le Havre</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Karaganda</t>
+          <t>Hyeres-Toulon</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>66.8</v>
+        <v>72.8</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -1283,104 +2084,104 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Gunma</t>
+          <t>K. Miyoshi vs M. Cassone</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Gunma</t>
+          <t>M. Cassone</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>59.3</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>Liga 2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Nagasaki vs Altiri Chiba</t>
+          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1388,43 +2189,43 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>64.09999999999999</v>
+        <v>59.1</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1434,43 +2235,43 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M. Cilic vs N. Basilashvili</t>
+          <t>T. Samuel vs Z. Bergs</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>N. Basilashvili</t>
+          <t>Z. Bergs</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.662</v>
+        <v>1.38</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>70.3</v>
+        <v>63.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1482,58 +2283,63 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+          <t>Karlovy Vary vs Kometa Brno</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>62.8</v>
+        <v>60.4</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1545,36 +2351,36 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1. Liga</t>
+          <t>FI1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
+          <t>SaiPa vs Karpat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>SaiPa</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1582,7 +2388,7 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>68.3</v>
+        <v>62.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -1591,17 +2397,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1613,36 +2419,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>League 1</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Ario Eslamshahr</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1650,67 +2456,62 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>65.3</v>
+        <v>49.4</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>SEW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>J. Fearnley vs H. Gaston</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>J. Fearnley</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.48</v>
+        <v>1.55</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1718,26 +2519,26 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>72.7</v>
+        <v>72.2</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1749,104 +2550,99 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>ECU</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>S. Kopp vs G. Cadenasso</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>G. Cadenasso</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>68.09999999999999</v>
+        <v>84.2</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>Beijing vs Guangdong</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.88</v>
+        <v>1.33</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1854,26 +2650,26 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>67.5</v>
+        <v>73.7</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1885,53 +2681,48 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>DE1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>M. Donald vs C. Sanchez Jover</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>68.90000000000001</v>
+        <v>83</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1941,75 +2732,70 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ERC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>R. M. Papoe vs O. Roca Batalla</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>R. M. Papoe</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>75.3</v>
+        <v>76.2</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2021,12 +2807,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -2036,16 +2822,16 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>S. Kartal vs K. Birrell</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>S. Kartal</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2053,7 +2839,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>74.5</v>
+        <v>70.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -2062,17 +2848,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2084,36 +2870,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>T. Valentova vs S. Zhang</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>T. Valentova</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2121,26 +2902,26 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>72.8</v>
+        <v>75.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2152,12 +2933,12 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2167,17 +2948,17 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>LBP</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Astros vs Mineros</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Astros</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2185,11 +2966,11 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>77.59999999999999</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2198,17 +2979,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2220,36 +3001,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>New York Islanders vs Anaheim Ducks</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.65</v>
+        <v>2.1</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2257,7 +3038,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>70.5</v>
+        <v>57.4</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2266,17 +3047,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2288,44 +3069,44 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Washington Capitals vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>71.7</v>
+        <v>74.5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -2334,17 +3115,17 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2356,36 +3137,36 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>Primera C Metropolitana</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>CA Lugano vs Cañuelas FC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Cañuelas FC</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
@@ -2393,67 +3174,62 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>64.3</v>
+        <v>55.7</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PT2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>A. Hernandez vs F. Ribero</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>A. Hernandez</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2461,11 +3237,11 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>65.59999999999999</v>
+        <v>72.5</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2475,24 +3251,24 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2502,26 +3278,26 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>DNW</t>
+          <t>KZ1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>Karaganda vs Gornyak Rudny</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>Karaganda</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2529,21 +3305,21 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>62.1</v>
+        <v>66.8</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2553,43 +3329,43 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>Utsunomiya Brex vs Gunma</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Gunma</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
@@ -2597,7 +3373,7 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>65.5</v>
+        <v>59.3</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
@@ -2606,17 +3382,17 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2628,12 +3404,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2643,21 +3419,21 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Nagasaki vs Altiri Chiba</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2665,7 +3441,7 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>66.09999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
@@ -2674,17 +3450,17 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2696,73 +3472,1350 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>M. Cilic vs N. Basilashvili</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>N. Basilashvili</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>B. Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>1. Liga</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Litvinov vs Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="G29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SEW</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Engelholm W vs Linkopings W</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Engelholm W</t>
+        </is>
+      </c>
+      <c r="G30" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Bojnice vs Voslauer</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bojnice</t>
+        </is>
+      </c>
+      <c r="G31" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AHL</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Ritten vs Asiago</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Ritten</t>
+        </is>
+      </c>
+      <c r="G32" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>DE1</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Flensburg-H.</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Section Paloise vs Leicester Tigers</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Section Paloise</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>C. Burel vs L. Romero Gormaz</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>C. Burel</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Canterbury vs Taranaki</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Canterbury</t>
+        </is>
+      </c>
+      <c r="G36" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Ada Blois vs La Rochelle</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Ada Blois</t>
+        </is>
+      </c>
+      <c r="G37" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G38" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G39" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G40" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G42" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G43" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G44" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E45" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="G45" t="n">
         <v>2</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I26" t="n">
+      <c r="I45" t="n">
         <v>56.3</v>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N26"/>
+  <autoFilter ref="A1:N45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$20</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -520,7 +520,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -535,21 +535,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Washington Capitals vs Los Angeles Kings</t>
+          <t>Grand Rapids Griffins vs Manitoba Moose</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Grand Rapids Griffins</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -557,7 +557,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>74.5</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -566,7 +566,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
+          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -576,7 +576,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -588,12 +588,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -603,21 +603,21 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>New York Islanders vs Anaheim Ducks</t>
+          <t>Rochester Americans vs Utica Comets</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>Utica Comets</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -625,94 +625,89 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>57.4</v>
+        <v>64.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>LBP</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Astros vs Mineros</t>
+          <t>L. Tararudee vs A. Krueger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Astros</t>
+          <t>A. Krueger</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>78.59999999999999</v>
+        <v>74.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -724,12 +719,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -739,16 +734,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>T. Valentova vs S. Zhang</t>
+          <t>J. D. Hara Friend vs J. McCabe</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>T. Valentova</t>
+          <t>J. D. Hara Friend</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -756,7 +751,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>75.8</v>
+        <v>63.4</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -765,17 +760,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -787,31 +782,36 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WE League</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>S. Kartal vs K. Birrell</t>
+          <t>Elfen Saitama W vs Vegalta Sendai W</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>S. Kartal</t>
+          <t>Elfen Saitama W</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.4</v>
+        <v>2.4</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -819,43 +819,43 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>70.5</v>
+        <v>53.4</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
+          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -865,33 +865,33 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>R. M. Papoe vs O. Roca Batalla</t>
+          <t>M. Bellucci vs T. M. Etcheverry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>R. M. Papoe</t>
+          <t>M. Bellucci</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>76.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -901,24 +901,24 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -928,24 +928,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>M. Donald vs C. Sanchez Jover</t>
+          <t>S. Cirstea vs S. Bejlek</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>M. Donald</t>
+          <t>S. Cirstea</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>83</v>
+        <v>62.8</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -954,17 +954,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -976,12 +976,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -991,21 +991,21 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Beijing vs Guangdong</t>
+          <t>Utsunomiya Brex vs Diamond Dolphins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Diamond Dolphins</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.33</v>
+        <v>1.45</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1013,16 +1013,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>73.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1032,87 +1032,92 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>S. Kopp vs G. Cadenasso</t>
+          <t>Qingdao vs Liaoning</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>G. Cadenasso</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>84.2</v>
+        <v>61.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1122,24 +1127,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>J. Fearnley vs H. Gaston</t>
+          <t>T. Monteiro vs H. Rocha</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>J. Fearnley</t>
+          <t>H. Rocha</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.43</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>72.2</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -1148,17 +1153,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1170,36 +1175,31 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>League 1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
+          <t>J. M. La Serna vs J. B. Torres</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr</t>
+          <t>J. M. La Serna</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2.5</v>
+        <v>1.48</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1207,94 +1207,94 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>49.4</v>
+        <v>75.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FI1</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>SaiPa vs Karpat</t>
+          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>SaiPa</t>
+          <t>Ittihad Alexandria</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>2.93</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>62.8</v>
+        <v>64.5</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1306,53 +1306,53 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>BH1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Karlovy Vary vs Kometa Brno</t>
+          <t>Nuwaidrad vs Al Ittihad</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>60.4</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
+          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1374,31 +1374,36 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>ICE</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>T. Samuel vs Z. Bergs</t>
+          <t>Black Wings Linz vs Vienna Capitals</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Z. Bergs</t>
+          <t>Black Wings Linz</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1406,26 +1411,26 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>63.3</v>
+        <v>58</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1437,36 +1442,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Liga 2</t>
+          <t>ULL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
+          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Black Dogs Budweis</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1474,7 +1479,7 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>59.1</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1483,17 +1488,17 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
+          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1505,63 +1510,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>K. Miyoshi vs M. Cassone</t>
+          <t>Lindemans Aalst vs Maaseik</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>M. Cassone</t>
+          <t>Maaseik</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>76.09999999999999</v>
+        <v>73.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1570,212 +1575,8 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Hyeres-Toulon vs Le Havre</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Hyeres-Toulon</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>72.8</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Tours vs Tourcoing</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Tours</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>75.7</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>5-0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-20</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>22:45</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>League One</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Notts County vs Sheffield Wednesday</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Sheffield Wednesday</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>60.4</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:N20"/>
+  <autoFilter ref="A1:N17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1786,7 +1587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1880,36 +1681,36 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>League One</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Notts County vs Sheffield Wednesday</t>
+          <t>Lindemans Aalst vs Maaseik</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Maaseik</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -1917,7 +1718,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>60.4</v>
+        <v>73.8</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1926,17 +1727,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1948,36 +1749,36 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FR1</t>
+          <t>ULL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Tours vs Tourcoing</t>
+          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tours</t>
+          <t>Black Dogs Budweis</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -1985,7 +1786,7 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>75.7</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1994,17 +1795,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
+          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -2016,44 +1817,44 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>ICE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon vs Le Havre</t>
+          <t>Black Wings Linz vs Vienna Capitals</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon</t>
+          <t>Black Wings Linz</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.38</v>
+        <v>1.88</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>72.8</v>
+        <v>58</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -2062,17 +1863,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -2084,44 +1885,44 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>BH1</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>K. Miyoshi vs M. Cassone</t>
+          <t>Nuwaidrad vs Al Ittihad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>M. Cassone</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>76.09999999999999</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -2130,17 +1931,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -2152,12 +1953,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2167,21 +1968,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Liga 2</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
+          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Ittihad Alexandria</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.1</v>
+        <v>2.93</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2189,26 +1990,26 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>59.1</v>
+        <v>64.5</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -2220,12 +2021,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -2235,16 +2036,16 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>T. Samuel vs Z. Bergs</t>
+          <t>J. M. La Serna vs J. B. Torres</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Z. Bergs</t>
+          <t>J. M. La Serna</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2252,7 +2053,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>63.3</v>
+        <v>75.8</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -2261,17 +2062,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -2283,36 +2084,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CEX</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Karlovy Vary vs Kometa Brno</t>
+          <t>T. Monteiro vs H. Rocha</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>H. Rocha</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.95</v>
+        <v>1.43</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -2320,26 +2116,26 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>60.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2351,44 +2147,44 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FI1</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>SaiPa vs Karpat</t>
+          <t>Qingdao vs Liaoning</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>SaiPa</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
@@ -2397,17 +2193,17 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2419,36 +2215,36 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>League 1</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
+          <t>Utsunomiya Brex vs Diamond Dolphins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr</t>
+          <t>Diamond Dolphins</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>2.5</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -2456,7 +2252,7 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>49.4</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -2465,17 +2261,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -2487,12 +2283,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2502,16 +2298,16 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>J. Fearnley vs H. Gaston</t>
+          <t>S. Cirstea vs S. Bejlek</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>J. Fearnley</t>
+          <t>S. Cirstea</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.55</v>
+        <v>1.4</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2519,7 +2315,7 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>72.2</v>
+        <v>62.8</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2528,17 +2324,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2550,12 +2346,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -2565,16 +2361,16 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>S. Kopp vs G. Cadenasso</t>
+          <t>M. Bellucci vs T. M. Etcheverry</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>G. Cadenasso</t>
+          <t>M. Bellucci</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.45</v>
+        <v>1.75</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -2582,7 +2378,7 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>84.2</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
@@ -2591,17 +2387,17 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -2613,36 +2409,36 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>WE League</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Beijing vs Guangdong</t>
+          <t>Elfen Saitama W vs Vegalta Sendai W</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Elfen Saitama W</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.33</v>
+        <v>2.4</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2650,43 +2446,43 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>73.7</v>
+        <v>53.4</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/6 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
+          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2696,24 +2492,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>M. Donald vs C. Sanchez Jover</t>
+          <t>J. D. Hara Friend vs J. McCabe</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>M. Donald</t>
+          <t>J. D. Hara Friend</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.65</v>
+        <v>1.45</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I14" t="n">
-        <v>83</v>
+        <v>63.4</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
@@ -2722,17 +2518,17 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2744,12 +2540,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -2759,16 +2555,16 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>R. M. Papoe vs O. Roca Batalla</t>
+          <t>L. Tararudee vs A. Krueger</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>R. M. Papoe</t>
+          <t>A. Krueger</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2776,7 +2572,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>76.2</v>
+        <v>74.3</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2785,17 +2581,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2807,31 +2603,36 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>S. Kartal vs K. Birrell</t>
+          <t>Rochester Americans vs Utica Comets</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>S. Kartal</t>
+          <t>Utica Comets</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>1.4</v>
+        <v>2.25</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2839,26 +2640,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>70.5</v>
+        <v>64.8</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2870,58 +2671,63 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>T. Valentova vs S. Zhang</t>
+          <t>Grand Rapids Griffins vs Manitoba Moose</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>T. Valentova</t>
+          <t>Grand Rapids Griffins</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.35</v>
+        <v>2.25</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>75.8</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2938,39 +2744,39 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LBP</t>
+          <t>League One</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Astros vs Mineros</t>
+          <t>Notts County vs Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Astros</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>78.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
@@ -2979,17 +2785,17 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -3006,31 +2812,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>FR1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>New York Islanders vs Anaheim Ducks</t>
+          <t>Tours vs Tourcoing</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -3038,31 +2844,31 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>57.4</v>
+        <v>75.7</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -3074,31 +2880,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Washington Capitals vs Los Angeles Kings</t>
+          <t>Hyeres-Toulon vs Le Havre</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Hyeres-Toulon</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>2</v>
+        <v>1.38</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -3106,7 +2912,7 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>74.5</v>
+        <v>72.8</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
@@ -3115,7 +2921,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
+          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -3137,75 +2943,75 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Primera C Metropolitana</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Lugano vs Cañuelas FC</t>
+          <t>K. Miyoshi vs M. Cassone</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cañuelas FC</t>
+          <t>M. Cassone</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>2.15</v>
+        <v>1.6</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>55.7</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3215,21 +3021,26 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Liga 2</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>A. Hernandez vs F. Ribero</t>
+          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>A. Hernandez</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -3237,26 +3048,26 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>72.5</v>
+        <v>59.1</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -3268,36 +3079,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>KZ1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Karaganda vs Gornyak Rudny</t>
+          <t>T. Samuel vs Z. Bergs</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Karaganda</t>
+          <t>Z. Bergs</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3305,7 +3111,7 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>66.8</v>
+        <v>63.3</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -3314,17 +3120,17 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -3336,53 +3142,53 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Gunma</t>
+          <t>Karlovy Vary vs Kometa Brno</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gunma</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.5</v>
+        <v>1.95</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>59.3</v>
+        <v>60.4</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3392,155 +3198,160 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>FI1</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Nagasaki vs Altiri Chiba</t>
+          <t>SaiPa vs Karpat</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>SaiPa</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.63</v>
+        <v>2</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>64.09999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>League 1</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>M. Cilic vs N. Basilashvili</t>
+          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>N. Basilashvili</t>
+          <t>Ario Eslamshahr</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1.662</v>
+        <v>2.5</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I26" t="n">
-        <v>70.3</v>
+        <v>49.4</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -3550,12 +3361,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+          <t>J. Fearnley vs H. Gaston</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp</t>
+          <t>J. Fearnley</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3567,7 +3378,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>62.8</v>
+        <v>72.2</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3576,17 +3387,17 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3598,36 +3409,31 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>1. Liga</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
+          <t>S. Kopp vs G. Cadenasso</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>G. Cadenasso</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3635,67 +3441,67 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>68.3</v>
+        <v>84.2</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>Beijing vs Guangdong</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>2.1</v>
+        <v>1.33</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3703,7 +3509,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>65.3</v>
+        <v>73.7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3712,17 +3518,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3734,63 +3540,58 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>SEW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>M. Donald vs C. Sanchez Jover</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.48</v>
+        <v>1.65</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>72.7</v>
+        <v>83</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3802,36 +3603,31 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>ECU</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>R. M. Papoe vs O. Roca Batalla</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>R. M. Papoe</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
@@ -3839,26 +3635,26 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>68.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3870,36 +3666,31 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>AHL</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>S. Kartal vs K. Birrell</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>S. Kartal</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.88</v>
+        <v>1.4</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3907,7 +3698,7 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>67.5</v>
+        <v>70.5</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3916,17 +3707,17 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3938,36 +3729,31 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>DE1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>T. Valentova vs S. Zhang</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>T. Valentova</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.7</v>
+        <v>1.35</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3975,67 +3761,67 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>68.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ERC</t>
+          <t>LBP</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>Astros vs Mineros</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Astros</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -4043,7 +3829,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>75.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -4052,17 +3838,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -4074,31 +3860,36 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>New York Islanders vs Anaheim Ducks</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
@@ -4106,75 +3897,75 @@
         </is>
       </c>
       <c r="I35" t="n">
-        <v>74.5</v>
+        <v>57.4</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>Washington Capitals vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>72.8</v>
+        <v>74.5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
@@ -4183,17 +3974,17 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4205,36 +3996,36 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>Primera C Metropolitana</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>CA Lugano vs Cañuelas FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Cañuelas FC</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.38</v>
+        <v>2.15</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4242,38 +4033,38 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>77.59999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4283,26 +4074,21 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PT2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>A. Hernandez vs F. Ribero</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>A. Hernandez</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.65</v>
+        <v>1.43</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
@@ -4310,67 +4096,67 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>70.5</v>
+        <v>72.5</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>KZ1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Karaganda vs Gornyak Rudny</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Karaganda</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4378,26 +4164,26 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>71.7</v>
+        <v>66.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4409,36 +4195,36 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Utsunomiya Brex vs Gunma</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Gunma</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
@@ -4446,16 +4232,16 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>64.3</v>
+        <v>59.3</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4465,24 +4251,24 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4492,21 +4278,21 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Nagasaki vs Altiri Chiba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.5</v>
+        <v>1.63</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4514,7 +4300,7 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>65.59999999999999</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
@@ -4523,17 +4309,17 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4545,104 +4331,94 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>DNW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>M. Cilic vs N. Basilashvili</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>N. Basilashvili</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.6</v>
+        <v>1.662</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>62.1</v>
+        <v>70.3</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PLW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>B. Van De Zandschulp</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4650,172 +4426,1255 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>65.5</v>
+        <v>62.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>1. Liga</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>66.09999999999999</v>
+        <v>68.3</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Litvinov vs Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="G45" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>SEW</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Engelholm W vs Linkopings W</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Engelholm W</t>
+        </is>
+      </c>
+      <c r="G46" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Bojnice vs Voslauer</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bojnice</t>
+        </is>
+      </c>
+      <c r="G47" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>AHL</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Ritten vs Asiago</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Ritten</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>DE1</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Flensburg-H.</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Section Paloise vs Leicester Tigers</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Section Paloise</t>
+        </is>
+      </c>
+      <c r="G50" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>C. Burel vs L. Romero Gormaz</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>C. Burel</t>
+        </is>
+      </c>
+      <c r="G51" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Canterbury vs Taranaki</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Canterbury</t>
+        </is>
+      </c>
+      <c r="G52" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I52" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Ada Blois vs La Rochelle</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Ada Blois</t>
+        </is>
+      </c>
+      <c r="G53" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I53" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I54" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G55" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I55" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G56" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I56" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G57" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I57" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G58" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I58" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G59" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I59" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G60" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I60" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="G61" t="n">
         <v>2</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
         <v>56.3</v>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N45"/>
+  <autoFilter ref="A1:N61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$N$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$N$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N17"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -443,6 +443,7 @@
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -516,6 +517,11 @@
           <t>Siła</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Forma sezon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1576,7 +1582,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N17"/>
+  <autoFilter ref="A1:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1587,7 +1593,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N61"/>
+  <dimension ref="A1:O61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1604,6 +1610,7 @@
     <col width="7" customWidth="1" min="12" max="12"/>
     <col width="9" customWidth="1" min="13" max="13"/>
     <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1677,6 +1684,11 @@
           <t>Siła</t>
         </is>
       </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Forma sezon</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -5674,7 +5686,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N61"/>
+  <autoFilter ref="A1:O61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$71</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -526,12 +526,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,29 +541,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>WHL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Grand Rapids Griffins vs Manitoba Moose</t>
+          <t>Prince George Cougars vs Vancouver Giants</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grand Rapids Griffins</t>
+          <t>Vancouver Giants</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>66.59999999999999</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,85 +572,85 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>WWWWW / LLDDW</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>AHL</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rochester Americans vs Utica Comets</t>
+          <t>K. Smith vs F. Sun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Utica Comets</t>
+          <t>K. Smith</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>2.25</v>
+        <v>1.5</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>64.8</v>
+        <v>75</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -658,16 +658,17 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -677,24 +678,24 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>L. Tararudee vs A. Krueger</t>
+          <t>M. Stoiana vs M. Uchijima</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>A. Krueger</t>
+          <t>M. Stoiana</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>74.3</v>
+        <v>75.2</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -703,17 +704,17 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -721,16 +722,17 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -740,16 +742,16 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend vs J. McCabe</t>
+          <t>V. Vacherot vs L. van Assche</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend</t>
+          <t>V. Vacherot</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.45</v>
+        <v>1.63</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -757,7 +759,7 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>63.4</v>
+        <v>63.5</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
@@ -766,17 +768,17 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
+          <t>LWLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -784,40 +786,41 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>WE League</t>
+          <t>FI2</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elfen Saitama W vs Vegalta Sendai W</t>
+          <t>Kiekko-Pojat vs Pyry</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Elfen Saitama W</t>
+          <t>Kiekko-Pojat</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -825,169 +828,194 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>53.4</v>
+        <v>72.3</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
+          <t>DWWWD (11 pkt) vs DLLLW (4 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4.0-1.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>DWWWD / DLLLW</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FIB</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>M. Bellucci vs T. M. Etcheverry</t>
+          <t>Levice vs Szolnoki Olaj</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>M. Bellucci</t>
+          <t>Levice</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.75</v>
+        <v>1.45</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>85.40000000000001</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
+          <t>WWWLD (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1.0-1.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>WWWLD / LLWLW</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>S. Cirstea vs S. Bejlek</t>
+          <t>Bayern vs Dubai</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>S. Cirstea</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.4</v>
+        <v>1.85</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>62.8</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs WLWWL (9 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2.0-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>WWWWL / WLWWL</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -997,152 +1025,167 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>NLE</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Diamond Dolphins</t>
+          <t>Siroki Brijeg vs Slovan Bratislava</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Diamond Dolphins</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>67.40000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>WWLWW / LLWLL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>PL2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qingdao vs Liaoning</t>
+          <t>AZS Poznan vs Bydgoszcz</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>AZS Poznan</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>61.8</v>
+        <v>76.7</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
+          <t>LWWWW (12 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>LWWWW / WLWLL</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>T. Monteiro vs H. Rocha</t>
+          <t>Besiktas vs Crystal Palace</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>H. Rocha</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.43</v>
+        <v>2.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1150,26 +1193,26 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>72.90000000000001</v>
+        <v>63.3</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLD (4 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1177,412 +1220,14 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>J. M. La Serna vs J. B. Torres</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>J. M. La Serna</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>75.8</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>2-0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Ittihad Alexandria</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>64.5</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>BH1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Nuwaidrad vs Al Ittihad</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Al Ittihad</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19:15</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>ICE</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Black Wings Linz vs Vienna Capitals</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Black Wings Linz</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>58</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>ULL</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Black Dogs Budweis</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>73.09999999999999</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>3-2</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-21</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>BE1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Lindemans Aalst vs Maaseik</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Maaseik</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>4-1</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>LWWLW / LLWD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O17"/>
+  <autoFilter ref="A1:O11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1593,7 +1238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O61"/>
+  <dimension ref="A1:O71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1693,44 +1338,44 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BE1</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Lindemans Aalst vs Maaseik</t>
+          <t>Besiktas vs Crystal Palace</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Maaseik</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>73.8</v>
+        <v>63.3</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1739,134 +1384,144 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLD (4 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>LWWLW / LLWD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>ULL</t>
+          <t>PL2</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
+          <t>AZS Poznan vs Bydgoszcz</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Black Dogs Budweis</t>
+          <t>AZS Poznan</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>73.09999999999999</v>
+        <v>76.7</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
+          <t>LWWWW (12 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>LWWWW / WLWLL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>NLE</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Black Wings Linz vs Vienna Capitals</t>
+          <t>Siroki Brijeg vs Slovan Bratislava</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Black Wings Linz</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>58</v>
+        <v>75.7</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
@@ -1875,34 +1530,39 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WWLWW / LLWLL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1912,89 +1572,94 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BH1</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Nuwaidrad vs Al Ittihad</t>
+          <t>Bayern vs Dubai</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>71.90000000000001</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs WLWWL (9 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2.0-0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WWWWL / WLWWL</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>FIB</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
+          <t>Levice vs Szolnoki Olaj</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ittihad Alexandria</t>
+          <t>Levice</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>2.93</v>
+        <v>1.45</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -2002,62 +1667,72 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>64.5</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWLD (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>1.0-1.0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>WWWLD / LLWLW</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FI2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>J. M. La Serna vs J. B. Torres</t>
+          <t>Kiekko-Pojat vs Pyry</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>J. M. La Serna</t>
+          <t>Kiekko-Pojat</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -2065,38 +1740,43 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>75.8</v>
+        <v>72.3</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>DWWWD (11 pkt) vs DLLLW (4 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>4.0-1.0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>DWWWD / DLLLW</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2111,24 +1791,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>T. Monteiro vs H. Rocha</t>
+          <t>V. Vacherot vs L. van Assche</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>H. Rocha</t>
+          <t>V. Vacherot</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.43</v>
+        <v>1.63</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I8" t="n">
-        <v>72.90000000000001</v>
+        <v>63.5</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
@@ -2137,17 +1817,17 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
+          <t>LWLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -2155,67 +1835,63 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CBA</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Qingdao vs Liaoning</t>
+          <t>M. Stoiana vs M. Uchijima</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>M. Stoiana</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>61.8</v>
+        <v>75.2</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -2223,103 +1899,105 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>BLJ</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Diamond Dolphins</t>
+          <t>K. Smith vs F. Sun</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Diamond Dolphins</t>
+          <t>K. Smith</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>67.40000000000001</v>
+        <v>75</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WHL</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>S. Cirstea vs S. Bejlek</t>
+          <t>Prince George Cougars vs Vancouver Giants</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>S. Cirstea</t>
+          <t>Vancouver Giants</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2327,31 +2005,36 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>62.8</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>WWWWW / LLDDW</t>
         </is>
       </c>
     </row>
@@ -2363,58 +2046,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BE1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>M. Bellucci vs T. M. Etcheverry</t>
+          <t>Lindemans Aalst vs Maaseik</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>M. Bellucci</t>
+          <t>Maaseik</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.75</v>
+        <v>1.3</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>85.40000000000001</v>
+        <v>73.8</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -2426,31 +2114,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>WE League</t>
+          <t>ULL</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Elfen Saitama W vs Vegalta Sendai W</t>
+          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Elfen Saitama W</t>
+          <t>Black Dogs Budweis</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -2458,31 +2146,31 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>53.4</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
+          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -2494,26 +2182,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ICE</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend vs J. McCabe</t>
+          <t>Black Wings Linz vs Vienna Capitals</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend</t>
+          <t>Black Wings Linz</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.45</v>
+        <v>1.88</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2521,26 +2214,26 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>63.4</v>
+        <v>58</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2557,26 +2250,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>BH1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>L. Tararudee vs A. Krueger</t>
+          <t>Nuwaidrad vs Al Ittihad</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>A. Krueger</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -2584,7 +2282,7 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>74.3</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
@@ -2593,17 +2291,17 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
+          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2620,31 +2318,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Rochester Americans vs Utica Comets</t>
+          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Utica Comets</t>
+          <t>Ittihad Alexandria</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.25</v>
+        <v>2.93</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -2652,26 +2350,26 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>64.8</v>
+        <v>64.5</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2688,58 +2386,53 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>AHL</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grand Rapids Griffins vs Manitoba Moose</t>
+          <t>J. M. La Serna vs J. B. Torres</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Grand Rapids Griffins</t>
+          <t>J. M. La Serna</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>2.25</v>
+        <v>1.48</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>66.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2751,63 +2444,58 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>League One</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Notts County vs Sheffield Wednesday</t>
+          <t>T. Monteiro vs H. Rocha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>H. Rocha</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>2.15</v>
+        <v>1.43</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>60.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2819,36 +2507,36 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FR1</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Tours vs Tourcoing</t>
+          <t>Qingdao vs Liaoning</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tours</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2856,7 +2544,7 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>75.7</v>
+        <v>61.8</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
@@ -2865,17 +2553,17 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2887,12 +2575,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2902,38 +2590,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon vs Le Havre</t>
+          <t>Utsunomiya Brex vs Diamond Dolphins</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon</t>
+          <t>Diamond Dolphins</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I20" t="n">
-        <v>72.8</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2943,24 +2631,24 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2968,31 +2656,26 @@
           <t>tennis</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>USC</t>
-        </is>
-      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>K. Miyoshi vs M. Cassone</t>
+          <t>S. Cirstea vs S. Bejlek</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>M. Cassone</t>
+          <t>S. Cirstea</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>76.09999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -3001,7 +2684,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3011,7 +2694,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -3023,53 +2706,48 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Liga 2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
+          <t>M. Bellucci vs T. M. Etcheverry</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>M. Bellucci</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I22" t="n">
-        <v>59.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3079,43 +2757,48 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>WE League</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>T. Samuel vs Z. Bergs</t>
+          <t>Elfen Saitama W vs Vegalta Sendai W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Z. Bergs</t>
+          <t>Elfen Saitama W</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>1.38</v>
+        <v>2.4</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -3123,94 +2806,89 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>63.3</v>
+        <v>53.4</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/6 za</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>CEX</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Karlovy Vary vs Kometa Brno</t>
+          <t>J. D. Hara Friend vs J. McCabe</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>J. D. Hara Friend</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.95</v>
+        <v>1.45</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>60.4</v>
+        <v>63.4</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -3222,63 +2900,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FI1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>SaiPa vs Karpat</t>
+          <t>L. Tararudee vs A. Krueger</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>SaiPa</t>
+          <t>A. Krueger</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I25" t="n">
-        <v>62.8</v>
+        <v>74.3</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3290,36 +2963,36 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>League 1</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
+          <t>Rochester Americans vs Utica Comets</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr</t>
+          <t>Utica Comets</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3327,89 +3000,94 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>49.4</v>
+        <v>64.8</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>J. Fearnley vs H. Gaston</t>
+          <t>Grand Rapids Griffins vs Manitoba Moose</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>J. Fearnley</t>
+          <t>Grand Rapids Griffins</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I27" t="n">
-        <v>72.2</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
+          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -3426,58 +3104,63 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>League One</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>S. Kopp vs G. Cadenasso</t>
+          <t>Notts County vs Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>G. Cadenasso</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1.45</v>
+        <v>2.15</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>84.2</v>
+        <v>60.4</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
+          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -3489,31 +3172,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>FR1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Beijing vs Guangdong</t>
+          <t>Tours vs Tourcoing</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
@@ -3521,7 +3204,7 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>73.7</v>
+        <v>75.7</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3530,17 +3213,17 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3557,26 +3240,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>M. Donald vs C. Sanchez Jover</t>
+          <t>Hyeres-Toulon vs Le Havre</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>M. Donald</t>
+          <t>Hyeres-Toulon</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.65</v>
+        <v>1.38</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3584,26 +3272,26 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>83</v>
+        <v>72.8</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3620,7 +3308,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -3628,26 +3316,31 @@
           <t>tennis</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>USC</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>R. M. Papoe vs O. Roca Batalla</t>
+          <t>K. Miyoshi vs M. Cassone</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>R. M. Papoe</t>
+          <t>M. Cassone</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>76.2</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
@@ -3656,7 +3349,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3666,7 +3359,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3683,26 +3376,31 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Liga 2</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>S. Kartal vs K. Birrell</t>
+          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>S. Kartal</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
@@ -3710,26 +3408,26 @@
         </is>
       </c>
       <c r="I32" t="n">
-        <v>70.5</v>
+        <v>59.1</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3746,7 +3444,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -3756,16 +3454,16 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>T. Valentova vs S. Zhang</t>
+          <t>T. Samuel vs Z. Bergs</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>T. Valentova</t>
+          <t>Z. Bergs</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3773,7 +3471,7 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>75.8</v>
+        <v>63.3</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
@@ -3782,7 +3480,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3792,7 +3490,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3809,31 +3507,31 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LBP</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Astros vs Mineros</t>
+          <t>Karlovy Vary vs Kometa Brno</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Astros</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
@@ -3841,7 +3539,7 @@
         </is>
       </c>
       <c r="I34" t="n">
-        <v>78.59999999999999</v>
+        <v>60.4</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3850,17 +3548,17 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3877,7 +3575,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -3887,38 +3585,38 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>FI1</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>New York Islanders vs Anaheim Ducks</t>
+          <t>SaiPa vs Karpat</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>SaiPa</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>57.4</v>
+        <v>62.8</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
+          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3928,12 +3626,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
@@ -3945,99 +3643,94 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>League 1</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Washington Capitals vs Los Angeles Kings</t>
+          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Ario Eslamshahr</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>74.5</v>
+        <v>49.4</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
+          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Primera C Metropolitana</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>CA Lugano vs Cañuelas FC</t>
+          <t>J. Fearnley vs H. Gaston</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Cañuelas FC</t>
+          <t>J. Fearnley</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>2.15</v>
+        <v>1.55</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
@@ -4045,43 +3738,43 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>55.7</v>
+        <v>72.2</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -4091,84 +3784,84 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>A. Hernandez vs F. Ribero</t>
+          <t>S. Kopp vs G. Cadenasso</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>A. Hernandez</t>
+          <t>G. Cadenasso</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>72.5</v>
+        <v>84.2</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KZ1</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Karaganda vs Gornyak Rudny</t>
+          <t>Beijing vs Guangdong</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Karaganda</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -4176,26 +3869,26 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>66.8</v>
+        <v>73.7</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4207,104 +3900,94 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>BLJ</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Gunma</t>
+          <t>M. Donald vs C. Sanchez Jover</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gunma</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>59.3</v>
+        <v>83</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BLJ</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nagasaki vs Altiri Chiba</t>
+          <t>R. M. Papoe vs O. Roca Batalla</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>R. M. Papoe</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -4312,43 +3995,43 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>64.09999999999999</v>
+        <v>76.2</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4358,43 +4041,43 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>M. Cilic vs N. Basilashvili</t>
+          <t>S. Kartal vs K. Birrell</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>N. Basilashvili</t>
+          <t>S. Kartal</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.662</v>
+        <v>1.4</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>70.3</v>
+        <v>70.5</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4406,12 +4089,12 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -4421,16 +4104,16 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+          <t>T. Valentova vs S. Zhang</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp</t>
+          <t>T. Valentova</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.55</v>
+        <v>1.35</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4438,7 +4121,7 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>62.8</v>
+        <v>75.8</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
@@ -4447,7 +4130,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4457,7 +4140,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4469,36 +4152,36 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>04:15</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>1. Liga</t>
+          <t>LBP</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
+          <t>Astros vs Mineros</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Astros</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>2.15</v>
+        <v>1.38</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
@@ -4506,7 +4189,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>68.3</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
@@ -4515,17 +4198,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4537,12 +4220,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -4552,17 +4235,17 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>New York Islanders vs Anaheim Ducks</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>New York Islanders</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -4574,16 +4257,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>65.3</v>
+        <v>57.4</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4593,56 +4276,56 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>65%</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>Washington Capitals vs Los Angeles Kings</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Washington Capitals</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>72.7</v>
+        <v>74.5</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4651,7 +4334,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4661,7 +4344,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4673,36 +4356,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>Primera C Metropolitana</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>CA Lugano vs Cañuelas FC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>Cañuelas FC</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>1.6</v>
+        <v>2.15</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4710,67 +4393,62 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>68.09999999999999</v>
+        <v>55.7</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>AHL</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>A. Hernandez vs F. Ribero</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>A. Hernandez</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.88</v>
+        <v>1.43</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4778,7 +4456,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>67.5</v>
+        <v>72.5</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4787,17 +4465,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>76%</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4809,36 +4487,36 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DE1</t>
+          <t>KZ1</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>Karaganda vs Gornyak Rudny</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>Karaganda</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
@@ -4846,130 +4524,135 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>68.90000000000001</v>
+        <v>66.8</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ERC</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>Utsunomiya Brex vs Gunma</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Gunma</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.63</v>
+        <v>1.5</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I50" t="n">
-        <v>75.3</v>
+        <v>59.3</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>54%</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>Nagasaki vs Altiri Chiba</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>Nagasaki</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.35</v>
+        <v>1.63</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4977,94 +4660,89 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>74.5</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>NPC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>M. Cilic vs N. Basilashvili</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>N. Basilashvili</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.43</v>
+        <v>1.662</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>72.8</v>
+        <v>70.3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5076,36 +4754,31 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>FR2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>B. Van De Zandschulp</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -5113,26 +4786,26 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>77.59999999999999</v>
+        <v>62.8</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5144,104 +4817,104 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>1. Liga</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>Lechia Gdansk</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>1.65</v>
+        <v>2.15</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>70.5</v>
+        <v>68.3</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LNB</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>Litvinov vs Karlovy Vary</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -5249,7 +4922,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>71.7</v>
+        <v>65.3</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -5258,17 +4931,17 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -5280,36 +4953,36 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>SEW</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Engelholm W vs Linkopings W</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Engelholm W</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -5317,7 +4990,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>64.3</v>
+        <v>72.7</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -5326,17 +4999,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5348,36 +5021,36 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>PT2</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>Bojnice vs Voslauer</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>Bojnice</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
@@ -5385,67 +5058,67 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>65.59999999999999</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>DNW</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>Ritten vs Asiago</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>Ritten</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.6</v>
+        <v>1.88</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
@@ -5453,21 +5126,21 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>62.1</v>
+        <v>67.5</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -5477,43 +5150,43 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>Flensburg-H.</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -5521,7 +5194,7 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>65.5</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
@@ -5530,17 +5203,17 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -5552,141 +5225,816 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>AUW</t>
+          <t>ERC</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>Section Paloise vs Leicester Tigers</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>Section Paloise</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.4</v>
+        <v>1.63</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>66.09999999999999</v>
+        <v>75.3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>C. Burel vs L. Romero Gormaz</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>C. Burel</t>
+        </is>
+      </c>
+      <c r="G61" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I61" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>Canterbury vs Taranaki</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Canterbury</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I62" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B61" t="inlineStr">
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>Ada Blois vs La Rochelle</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Ada Blois</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G65" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I66" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G67" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I67" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G68" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I68" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G69" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I69" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G70" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I70" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C61" t="inlineStr">
+      <c r="C71" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
+      <c r="D71" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="E71" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F71" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G61" t="n">
+      <c r="G71" t="n">
         <v>2</v>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I61" t="n">
+      <c r="I71" t="n">
         <v>56.3</v>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="J71" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="L71" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="M71" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="N71" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O61"/>
+  <autoFilter ref="A1:O71"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$11</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$71</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$98</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -526,12 +526,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -541,21 +541,21 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WHL</t>
+          <t>OHL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Prince George Cougars vs Vancouver Giants</t>
+          <t>Brampton Steelheads vs Brantford Bulldogs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vancouver Giants</t>
+          <t>Brantford Bulldogs</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -563,7 +563,7 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>64.40000000000001</v>
+        <v>65.7</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -572,7 +572,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLDDW (5 pkt)</t>
+          <t>WWDLL (7 pkt) vs WLLDD (5 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -592,38 +592,43 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>WWWWW / LLDDW</t>
+          <t>WWDLL / WLLDD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>K. Smith vs F. Sun</t>
+          <t>Grand Rapids Griffins vs Cleveland Monsters</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>K. Smith</t>
+          <t>Grand Rapids Griffins</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.5</v>
+        <v>2.15</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -631,26 +636,26 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWWDD (8 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>1.0-0</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -658,100 +663,118 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>WWWWL / LWWDD</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>QMJ</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>M. Stoiana vs M. Uchijima</t>
+          <t>Rouyn-Noranda Huskies vs Quebec Remparts</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>M. Stoiana</t>
+          <t>Quebec Remparts</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.58</v>
+        <v>1.9</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>75.2</v>
+        <v>60.6</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>WLWWW (12 pkt) vs DLWWL (7 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>1.0-0</t>
+          <t>1.5-1.5</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>WLWWW / DLWWL</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>V. Vacherot vs L. van Assche</t>
+          <t>Vancouver Canucks vs Detroit Red Wings</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>V. Vacherot</t>
+          <t>Detroit Red Wings</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.63</v>
+        <v>1.95</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -759,26 +782,26 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>63.5</v>
+        <v>71.8</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs WLLLW (6 pkt)</t>
+          <t>WDDWD (9 pkt) vs LLLDL (1 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>3.0-0</t>
+          <t>3.5-0.5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -786,49 +809,53 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>WDDWD / LLLDL</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FI2</t>
+          <t>LMP</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kiekko-Pojat vs Pyry</t>
+          <t>Hermosillo vs Jaguares de Nayarit</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kiekko-Pojat</t>
+          <t>Hermosillo</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.5</v>
+        <v>1.581</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I6" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
@@ -837,7 +864,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>DWWWD (11 pkt) vs DLLLW (4 pkt)</t>
+          <t>WWWL (9 pkt) vs LLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -847,7 +874,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -857,43 +884,38 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>DWWWD / DLLLW</t>
+          <t xml:space="preserve"> / LLLLL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>FIB</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Levice vs Szolnoki Olaj</t>
+          <t>A. Li vs L. Tagger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Levice</t>
+          <t>A. Li</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.45</v>
+        <v>1.62</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -901,72 +923,63 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>66.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>WWWLD (10 pkt) vs LLWLW (6 pkt)</t>
+          <t>WWWLW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>WWWLD / LLWLW</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>EUR</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Bayern vs Dubai</t>
+          <t>M. Donald vs F. Romano</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.85</v>
+        <v>1.73</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -974,26 +987,26 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>69.90000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs WLWWL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLW (9 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>2.0-0</t>
+          <t>5.0-0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1001,45 +1014,36 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>WWWWL / WLWWL</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>NLE</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Siroki Brijeg vs Slovan Bratislava</t>
+          <t>F. Misolic vs M. Ribecai</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Siroki Brijeg</t>
+          <t>F. Misolic</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.6</v>
+        <v>1.68</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1047,16 +1051,16 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>75.7</v>
+        <v>69</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>WWWWL (12 pkt) vs WWLLW (9 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1066,7 +1070,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1074,72 +1078,68 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>WWLWW / LLWLL</t>
-        </is>
-      </c>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PL2</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AZS Poznan vs Bydgoszcz</t>
+          <t>Wei Chuan Dragons vs Chinatrust Brothers</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>AZS Poznan</t>
+          <t>Wei Chuan Dragons</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.35</v>
+        <v>1.662</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>76.7</v>
+        <v>62.5</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WLWLL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>4.0-0</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1149,19 +1149,19 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>LWWWW / WLWLL</t>
+          <t>LWWWW / WLLLW</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1171,63 +1171,1258 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>V-League</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Besiktas vs Crystal Palace</t>
+          <t>Hoang Anh Gia Lai vs Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>55.9</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>WWWLL (9 pkt) vs LWLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>FIU</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Jukurit U20 vs Vaasan Sport U20</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Jukurit U20</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1.581</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>WWLLW (9 pkt) vs WLLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>RU2</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Orsk vs Metallurg Novokuznetsk</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Metallurg Novokuznetsk</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1.725</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>LWWWW (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Litvinov vs Plzen</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Plzen</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>DLWDW (8 pkt) vs WLLWD (7 pkt)</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>DLWDW / WLLWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Kladno vs Pardubice</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pardubice</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>74.90000000000001</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>WDDWW (11 pkt) vs WLLWD (7 pkt)</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>4.0-0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>WDDWW / WLLWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>FIU</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Kiekko-Espoo U20 vs Jokerit U20</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Kiekko-Espoo U20</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>1.538</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>66.3</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>WLWLW (9 pkt) vs LLLLW (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>FI1</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Kiekko-Espoo vs IFK Helsinki</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kiekko-Espoo</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>66</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>WLLWD (7 pkt) vs DLDWD (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>3.5-0.5</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>WLLWD / DLDWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>A. Fils vs A. Michelsen</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>A. Fils</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>WLWLW (9 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>2.0-0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>SES</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Boras vs Tranas</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Boras</t>
+        </is>
+      </c>
+      <c r="G19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>72</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs DLWLW (7 pkt)</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>4.0-0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>LWWLW / DLWLW</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>F. Cobolli vs B. Nakashima</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>B. Nakashima</t>
+        </is>
+      </c>
+      <c r="G20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>65.8</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>WWLWL (9 pkt) vs WLLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0.5-0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>DE2</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Bad Nauheim vs Landshut</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Landshut</t>
+        </is>
+      </c>
+      <c r="G21" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>55</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>4/6 za</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>WWWLL (9 pkt) vs WLDLL (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>2.0-2.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>WWWLL / WLDLL</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>DE1</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Grizzly Wolfsburg vs ERC Ingolstadt</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ERC Ingolstadt</t>
+        </is>
+      </c>
+      <c r="G22" t="n">
         <v>2.1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>63.3</v>
-      </c>
-      <c r="J11" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>65.90000000000001</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>WWDDW (11 pkt) vs LLDDL (2 pkt)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>3.5-1.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>WWDDW / LLDDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>DE2</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Coburg 2000 vs Minden</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Minden</t>
+        </is>
+      </c>
+      <c r="G23" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J23" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>LWWLW (9 pkt) vs LLWLD (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>3.0-0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>LWWLW / LLWD</t>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>WWWLW (12 pkt) vs LLDDL (2 pkt)</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0.5-0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>WWWLW / LLDDL</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Olympiacos vs Fenerbahce</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Olympiacos</t>
+        </is>
+      </c>
+      <c r="G24" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWWWL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>20:45</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PRR</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Newcastle Red Bulls vs Sale Sharks</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Sale Sharks</t>
+        </is>
+      </c>
+      <c r="G25" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>62</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>LWWLL (6 pkt) vs LLLLW (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>1.5-1.5</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>LWWLL / LLLLW</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>21:30</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Stars League</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Al Jolan SC vs Kahraba Baghdad</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Al Jolan SC</t>
+        </is>
+      </c>
+      <c r="G26" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
+        <v>49.3</v>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>3/4 za</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>WLWLW (9 pkt) vs LWLWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Eerste Divisie</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>TOP Oss vs Jong Ajax</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>TOP Oss</t>
+        </is>
+      </c>
+      <c r="G27" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>51.8</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>3/4 za</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Ekstraklasa</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Widzew Lodz vs Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Gornik Zabrze</t>
+        </is>
+      </c>
+      <c r="G28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>55</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>DWLDW (8 pkt) vs DLDDD (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1.0-0</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>DWDW / DLDD</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O28"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1238,7 +2433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O71"/>
+  <dimension ref="A1:O98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1338,12 +2533,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>22:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1353,29 +2548,29 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Europa League</t>
+          <t>Ekstraklasa</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Besiktas vs Crystal Palace</t>
+          <t>Widzew Lodz vs Gornik Zabrze</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Besiktas</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>63.3</v>
+        <v>55</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
@@ -1384,17 +2579,17 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLD (4 pkt)</t>
+          <t>DWLDW (8 pkt) vs DLDDD (4 pkt)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>3.0-0</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>57%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -1404,238 +2599,230 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>LWWLW / LLWD</t>
+          <t>DWDW / DLDD</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PL2</t>
+          <t>Eerste Divisie</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AZS Poznan vs Bydgoszcz</t>
+          <t>TOP Oss vs Jong Ajax</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>AZS Poznan</t>
+          <t>TOP Oss</t>
         </is>
       </c>
       <c r="G3" t="n">
-        <v>1.35</v>
+        <v>2.08</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I3" t="n">
-        <v>76.7</v>
+        <v>51.8</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>3/4 za</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WLWLL (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>4.0-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>LWWWW / WLWLL</t>
-        </is>
-      </c>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NLE</t>
+          <t>Stars League</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Siroki Brijeg vs Slovan Bratislava</t>
+          <t>Al Jolan SC vs Kahraba Baghdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Siroki Brijeg</t>
+          <t>Al Jolan SC</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1.6</v>
+        <v>2.47</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I4" t="n">
-        <v>75.7</v>
+        <v>49.3</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>3/4 za</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWLW (9 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>4.0-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>WWLWW / LLWLL</t>
-        </is>
-      </c>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:45</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>rugby</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>PRR</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Bayern vs Dubai</t>
+          <t>Newcastle Red Bulls vs Sale Sharks</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dubai</t>
+          <t>Sale Sharks</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>1.85</v>
+        <v>1.45</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I5" t="n">
-        <v>69.90000000000001</v>
+        <v>62</v>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs WLWWL (9 pkt)</t>
+          <t>LWWLL (6 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>2.0-0</t>
+          <t>1.5-1.5</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>WWWWL / WLWWL</t>
+          <t>LWWLL / LLLLW</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1645,21 +2832,21 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FIB</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Levice vs Szolnoki Olaj</t>
+          <t>Olympiacos vs Fenerbahce</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Levice</t>
+          <t>Olympiacos</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1.45</v>
+        <v>1.64</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -1667,72 +2854,68 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>66.40000000000001</v>
+        <v>68.7</v>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>WWWLD (10 pkt) vs LLWLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWWWL (9 pkt)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>WWWLD / LLWLW</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>handball</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FI2</t>
+          <t>DE2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kiekko-Pojat vs Pyry</t>
+          <t>Coburg 2000 vs Minden</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kiekko-Pojat</t>
+          <t>Minden</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -1740,7 +2923,7 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>72.3</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
@@ -1749,17 +2932,17 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>DWWWD (11 pkt) vs DLLLW (4 pkt)</t>
+          <t>WWWLW (12 pkt) vs LLDDL (2 pkt)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>4.0-1.0</t>
+          <t>0.5-0</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1769,38 +2952,43 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>DWWWD / DLLLW</t>
+          <t>WWWLW / LLDDL</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>DE1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>V. Vacherot vs L. van Assche</t>
+          <t>Grizzly Wolfsburg vs ERC Ingolstadt</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>V. Vacherot</t>
+          <t>ERC Ingolstadt</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>1.63</v>
+        <v>2.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1808,108 +2996,121 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>63.5</v>
+        <v>65.90000000000001</v>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWDDW (11 pkt) vs LLDDL (2 pkt)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>3.0-0</t>
+          <t>3.5-1.0</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>WWDDW / LLDDL</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06:25</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>DE2</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>M. Stoiana vs M. Uchijima</t>
+          <t>Bad Nauheim vs Landshut</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>M. Stoiana</t>
+          <t>Landshut</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1.58</v>
+        <v>2</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I9" t="n">
-        <v>75.2</v>
+        <v>55</v>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/6 za</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>WWWLL (9 pkt) vs WLDLL (4 pkt)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>1.0-0</t>
+          <t>2.0-2.0</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>45%</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>WWWLL / WLDLL</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06:10</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1919,24 +3120,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>K. Smith vs F. Sun</t>
+          <t>F. Cobolli vs B. Nakashima</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>K. Smith</t>
+          <t>B. Nakashima</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I10" t="n">
-        <v>75</v>
+        <v>65.8</v>
       </c>
       <c r="J10" t="inlineStr">
         <is>
@@ -1945,17 +3146,17 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWLWL (9 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>1.0-0</t>
+          <t>0.5-0</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1968,12 +3169,12 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>04:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1983,29 +3184,29 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>WHL</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Prince George Cougars vs Vancouver Giants</t>
+          <t>Boras vs Tranas</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vancouver Giants</t>
+          <t>Boras</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I11" t="n">
-        <v>64.40000000000001</v>
+        <v>72</v>
       </c>
       <c r="J11" t="inlineStr">
         <is>
@@ -2014,17 +3215,17 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLDDW (5 pkt)</t>
+          <t>LWWLW (9 pkt) vs DLWLW (7 pkt)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>3.0-2.0</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -2034,65 +3235,60 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>WWWWW / LLDDW</t>
+          <t>LWWLW / DLWLW</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BE1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Lindemans Aalst vs Maaseik</t>
+          <t>A. Fils vs A. Michelsen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Maaseik</t>
+          <t>A. Fils</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I12" t="n">
-        <v>73.8</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
+          <t>WLWLW (9 pkt) vs WWLLL (6 pkt)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2.0-0</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -2105,16 +3301,17 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -2124,29 +3321,29 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ULL</t>
+          <t>FI1</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
+          <t>Kiekko-Espoo vs IFK Helsinki</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Black Dogs Budweis</t>
+          <t>Kiekko-Espoo</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I13" t="n">
-        <v>73.09999999999999</v>
+        <v>66</v>
       </c>
       <c r="J13" t="inlineStr">
         <is>
@@ -2155,34 +3352,39 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
+          <t>WLLWD (7 pkt) vs DLDWD (6 pkt)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3.5-0.5</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>WLLWD / DLDWD</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19:15</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -2192,21 +3394,21 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>ICE</t>
+          <t>FIU</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Black Wings Linz vs Vienna Capitals</t>
+          <t>Kiekko-Espoo U20 vs Jokerit U20</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Black Wings Linz</t>
+          <t>Kiekko-Espoo U20</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1.88</v>
+        <v>1.538</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -2214,26 +3416,26 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>58</v>
+        <v>66.3</v>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
+          <t>WLWLW (9 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>78%</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2241,125 +3443,131 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>19:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>BH1</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Nuwaidrad vs Al Ittihad</t>
+          <t>Kladno vs Pardubice</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Pardubice</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I15" t="n">
-        <v>71.90000000000001</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
+          <t>WDDWW (11 pkt) vs WLLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>WDDWW / WLLWD</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Premier League</t>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
+          <t>Litvinov vs Plzen</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ittihad Alexandria</t>
+          <t>Plzen</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>2.93</v>
+        <v>2.15</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="I16" t="n">
-        <v>64.5</v>
+        <v>52.9</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>DLWDW (8 pkt) vs WLLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2369,43 +3577,53 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>DLWDW / WLLWD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>RU2</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>J. M. La Serna vs J. B. Torres</t>
+          <t>Orsk vs Metallurg Novokuznetsk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>J. M. La Serna</t>
+          <t>Metallurg Novokuznetsk</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1.48</v>
+        <v>1.725</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -2413,26 +3631,26 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>75.8</v>
+        <v>61.7</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWWLW (9 pkt)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2440,62 +3658,68 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>FIU</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>T. Monteiro vs H. Rocha</t>
+          <t>Jukurit U20 vs Vaasan Sport U20</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>H. Rocha</t>
+          <t>Jukurit U20</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>1.43</v>
+        <v>1.581</v>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I18" t="n">
-        <v>72.90000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
+          <t>WWLLW (9 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2503,40 +3727,41 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>V-League</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Qingdao vs Liaoning</t>
+          <t>Hoang Anh Gia Lai vs Song Lam Nghe An</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Qingdao</t>
+          <t>Song Lam Nghe An</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1.6</v>
+        <v>2.21</v>
       </c>
       <c r="H19" t="inlineStr">
         <is>
@@ -2544,26 +3769,26 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>61.8</v>
+        <v>55.9</v>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
+          <t>WWWLL (9 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2571,40 +3796,41 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>baseball</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>CPB</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Diamond Dolphins</t>
+          <t>Wei Chuan Dragons vs Chinatrust Brothers</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Diamond Dolphins</t>
+          <t>Wei Chuan Dragons</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1.45</v>
+        <v>1.662</v>
       </c>
       <c r="H20" t="inlineStr">
         <is>
@@ -2612,43 +3838,48 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>67.40000000000001</v>
+        <v>62.5</v>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
+          <t>LWWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>49%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>LWWWW / WLLLW</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -2658,24 +3889,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>S. Cirstea vs S. Bejlek</t>
+          <t>F. Misolic vs M. Ribecai</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>S. Cirstea</t>
+          <t>F. Misolic</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>1.4</v>
+        <v>1.68</v>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I21" t="n">
-        <v>62.8</v>
+        <v>69</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
@@ -2684,17 +3915,17 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs WWLLW (9 pkt)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2702,16 +3933,17 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -2721,16 +3953,16 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>M. Bellucci vs T. M. Etcheverry</t>
+          <t>M. Donald vs F. Romano</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>M. Bellucci</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
@@ -2738,67 +3970,63 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>85.40000000000001</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WWLLW (9 pkt)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>5.0-0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>WE League</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Elfen Saitama W vs Vegalta Sendai W</t>
+          <t>A. Li vs L. Tagger</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Elfen Saitama W</t>
+          <t>A. Li</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
@@ -2806,125 +4034,141 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>53.4</v>
+        <v>68.5</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>4/6 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
+          <t>WWWLW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>04:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>baseball</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LMP</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend vs J. McCabe</t>
+          <t>Hermosillo vs Jaguares de Nayarit</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>J. D. Hara Friend</t>
+          <t>Hermosillo</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>1.45</v>
+        <v>1.581</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I24" t="n">
-        <v>63.4</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
+          <t>WWWL (9 pkt) vs LLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>3-0</t>
+          <t>4.0-1.0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>89%</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> / LLLLL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NHL</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>L. Tararudee vs A. Krueger</t>
+          <t>Vancouver Canucks vs Detroit Red Wings</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>A. Krueger</t>
+          <t>Detroit Red Wings</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
@@ -2932,43 +4176,48 @@
         </is>
       </c>
       <c r="I25" t="n">
-        <v>74.3</v>
+        <v>71.8</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
+          <t>WDDWD (9 pkt) vs LLLDL (1 pkt)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>3.5-0.5</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>WDDWD / LLLDL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>01:05</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2978,21 +4227,21 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>QMJ</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rochester Americans vs Utica Comets</t>
+          <t>Rouyn-Noranda Huskies vs Quebec Remparts</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Utica Comets</t>
+          <t>Quebec Remparts</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>2.25</v>
+        <v>1.9</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
@@ -3000,38 +4249,43 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>64.8</v>
+        <v>60.6</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
+          <t>WLWWW (12 pkt) vs DLWWL (7 pkt)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>1.5-1.5</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>82%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>WLWWW / DLWWL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-10-21</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3051,7 +4305,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grand Rapids Griffins vs Manitoba Moose</t>
+          <t>Grand Rapids Griffins vs Cleveland Monsters</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3060,7 +4314,7 @@
         </is>
       </c>
       <c r="G27" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
@@ -3068,7 +4322,7 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>66.59999999999999</v>
+        <v>63</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
@@ -3077,12 +4331,12 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWWDD (8 pkt)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3093,42 +4347,47 @@
       <c r="N27" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>WWWWL / LWWDD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>22:45</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>League One</t>
+          <t>OHL</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Notts County vs Sheffield Wednesday</t>
+          <t>Brampton Steelheads vs Brantford Bulldogs</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Brantford Bulldogs</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
@@ -3136,7 +4395,7 @@
         </is>
       </c>
       <c r="I28" t="n">
-        <v>60.4</v>
+        <v>65.7</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
@@ -3145,66 +4404,71 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
+          <t>WWDLL (7 pkt) vs WLLDD (5 pkt)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>WWDLL / WLLDD</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>volleyball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FR1</t>
+          <t>Europa League</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tours vs Tourcoing</t>
+          <t>Besiktas vs Crystal Palace</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tours</t>
+          <t>Besiktas</t>
         </is>
       </c>
       <c r="G29" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>75.7</v>
+        <v>63.3</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
@@ -3213,58 +4477,63 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
+          <t>LWWLW (9 pkt) vs LLWLD (4 pkt)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>LWWLW / LLWD</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>PL2</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon vs Le Havre</t>
+          <t>AZS Poznan vs Bydgoszcz</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hyeres-Toulon</t>
+          <t>AZS Poznan</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
@@ -3272,63 +4541,68 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>72.8</v>
+        <v>76.7</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>LWWWW / WLWLL</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>USC</t>
+          <t>NLE</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>K. Miyoshi vs M. Cassone</t>
+          <t>Siroki Brijeg vs Slovan Bratislava</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>M. Cassone</t>
+          <t>Siroki Brijeg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -3340,75 +4614,80 @@
         </is>
       </c>
       <c r="I31" t="n">
-        <v>76.09999999999999</v>
+        <v>75.7</v>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
+          <t>WWLWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4.0-0</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>WWLWW / LLWLL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Liga 2</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
+          <t>Bayern vs Dubai</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Chindia Targoviste</t>
+          <t>Dubai</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>59.1</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="J32" t="inlineStr">
         <is>
@@ -3417,53 +4696,63 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
+          <t>WWWWL (12 pkt) vs WLWWL (9 pkt)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>2.0-0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>WWWWL / WLWWL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>FIB</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>T. Samuel vs Z. Bergs</t>
+          <t>Levice vs Szolnoki Olaj</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Z. Bergs</t>
+          <t>Levice</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
@@ -3471,43 +4760,48 @@
         </is>
       </c>
       <c r="I33" t="n">
-        <v>63.3</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWLD (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>1.0-1.0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>WWWLD / LLWLW</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3517,29 +4811,29 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>FI2</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Karlovy Vary vs Kometa Brno</t>
+          <t>Kiekko-Pojat vs Pyry</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Kiekko-Pojat</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>1.95</v>
+        <v>1.5</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>60.4</v>
+        <v>72.3</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3548,85 +4842,85 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
+          <t>DWWWD (11 pkt) vs DLLLW (4 pkt)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4.0-1.0</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>DWWWD / DLLLW</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>FI1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>SaiPa vs Karpat</t>
+          <t>V. Vacherot vs L. van Assche</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>SaiPa</t>
+          <t>V. Vacherot</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>2</v>
+        <v>1.63</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>62.8</v>
+        <v>63.5</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
+          <t>LWLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>3.0-0</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -3634,84 +4928,81 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>06:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>League 1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
+          <t>M. Stoiana vs M. Uchijima</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ario Eslamshahr</t>
+          <t>M. Stoiana</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>2.5</v>
+        <v>1.58</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>49.4</v>
+        <v>75.2</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>06:10</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -3721,24 +5012,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>J. Fearnley vs H. Gaston</t>
+          <t>K. Smith vs F. Sun</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>J. Fearnley</t>
+          <t>K. Smith</t>
         </is>
       </c>
       <c r="G37" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>72.2</v>
+        <v>75</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
@@ -3747,17 +5038,17 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1.0-0</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>86%</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3765,103 +5056,114 @@
           <t>⭐⭐⭐</t>
         </is>
       </c>
+      <c r="O37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>04:00</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>WHL</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>S. Kopp vs G. Cadenasso</t>
+          <t>Prince George Cougars vs Vancouver Giants</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>G. Cadenasso</t>
+          <t>Vancouver Giants</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>1.45</v>
+        <v>2</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I38" t="n">
-        <v>84.2</v>
+        <v>64.40000000000001</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0-0</t>
+          <t>3.0-2.0</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>WWWWW / LLDDW</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>volleyball</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>CBA</t>
+          <t>BE1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Beijing vs Guangdong</t>
+          <t>Lindemans Aalst vs Maaseik</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Beijing</t>
+          <t>Maaseik</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
@@ -3869,7 +5171,7 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>73.7</v>
+        <v>73.8</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
@@ -3878,7 +5180,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3888,7 +5190,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3900,58 +5202,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>20:15</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>ULL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>M. Donald vs C. Sanchez Jover</t>
+          <t>CZU Farmers Prague vs Black Dogs Budweis</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>M. Donald</t>
+          <t>Black Dogs Budweis</t>
         </is>
       </c>
       <c r="G40" t="n">
-        <v>1.65</v>
+        <v>1.5</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I40" t="n">
-        <v>83</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWWL (9 pkt) vs DLLLL (1 pkt)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3963,31 +5270,36 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>19:15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>ICE</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>R. M. Papoe vs O. Roca Batalla</t>
+          <t>Black Wings Linz vs Vienna Capitals</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>R. M. Papoe</t>
+          <t>Black Wings Linz</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>1.43</v>
+        <v>1.88</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
@@ -3995,26 +5307,26 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>76.2</v>
+        <v>58</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWLD (10 pkt)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4026,31 +5338,36 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>19:00</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>BH1</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>S. Kartal vs K. Birrell</t>
+          <t>Nuwaidrad vs Al Ittihad</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>S. Kartal</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
@@ -4058,7 +5375,7 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>70.5</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
@@ -4067,17 +5384,17 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
+          <t>DLWWW (10 pkt) vs LLWLW (6 pkt)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4089,31 +5406,36 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>04:40</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>Premier League</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>T. Valentova vs S. Zhang</t>
+          <t>Ghazl Al Mahalla vs Ittihad Alexandria</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>T. Valentova</t>
+          <t>Ittihad Alexandria</t>
         </is>
       </c>
       <c r="G43" t="n">
-        <v>1.35</v>
+        <v>2.93</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
@@ -4121,26 +5443,26 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>75.8</v>
+        <v>64.5</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/4 za</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>brak</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4152,63 +5474,58 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>04:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>LBP</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Astros vs Mineros</t>
+          <t>J. M. La Serna vs J. B. Torres</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Astros</t>
+          <t>J. M. La Serna</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I44" t="n">
-        <v>78.59999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -4220,112 +5537,107 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>NHL</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>New York Islanders vs Anaheim Ducks</t>
+          <t>T. Monteiro vs H. Rocha</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>New York Islanders</t>
+          <t>H. Rocha</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>2.1</v>
+        <v>1.43</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I45" t="n">
-        <v>57.4</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
+          <t>WLWWW (12 pkt) vs WLLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>01:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NHL</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Washington Capitals vs Los Angeles Kings</t>
+          <t>Qingdao vs Liaoning</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Washington Capitals</t>
+          <t>Qingdao</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>1.6</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I46" t="n">
-        <v>74.5</v>
+        <v>61.8</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
@@ -4334,7 +5646,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
+          <t>LWWWW (12 pkt) vs WWWDL (10 pkt)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4344,7 +5656,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -4356,36 +5668,36 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>22:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Primera C Metropolitana</t>
+          <t>BLJ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>CA Lugano vs Cañuelas FC</t>
+          <t>Utsunomiya Brex vs Diamond Dolphins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Cañuelas FC</t>
+          <t>Diamond Dolphins</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2.15</v>
+        <v>1.45</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
@@ -4393,7 +5705,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>55.7</v>
+        <v>67.40000000000001</v>
       </c>
       <c r="J47" t="inlineStr">
         <is>
@@ -4402,17 +5714,17 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
+          <t>WWWWW (15 pkt) vs WLLWW (9 pkt)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>49%</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -4424,12 +5736,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -4439,16 +5751,16 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>A. Hernandez vs F. Ribero</t>
+          <t>S. Cirstea vs S. Bejlek</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>A. Hernandez</t>
+          <t>S. Cirstea</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
@@ -4456,7 +5768,7 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>72.5</v>
+        <v>62.8</v>
       </c>
       <c r="J48" t="inlineStr">
         <is>
@@ -4465,17 +5777,17 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4487,104 +5799,99 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>KZ1</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karaganda vs Gornyak Rudny</t>
+          <t>M. Bellucci vs T. M. Etcheverry</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Karaganda</t>
+          <t>M. Bellucci</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>66.8</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLW (3 pkt)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>BLJ</t>
+          <t>WE League</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Utsunomiya Brex vs Gunma</t>
+          <t>Elfen Saitama W vs Vegalta Sendai W</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Gunma</t>
+          <t>Elfen Saitama W</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
@@ -4592,26 +5899,26 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>59.3</v>
+        <v>53.4</v>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>4/6 za</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>WWWDD (11 pkt) vs LLDDW (5 pkt)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>68%</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4623,36 +5930,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>BLJ</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nagasaki vs Altiri Chiba</t>
+          <t>J. D. Hara Friend vs J. McCabe</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Nagasaki</t>
+          <t>J. D. Hara Friend</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>1.63</v>
+        <v>1.45</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
@@ -4660,43 +5962,43 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>64.09999999999999</v>
+        <v>63.4</v>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWLW (9 pkt) vs WLWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>3-0</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4706,43 +6008,43 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>M. Cilic vs N. Basilashvili</t>
+          <t>L. Tararudee vs A. Krueger</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>N. Basilashvili</t>
+          <t>A. Krueger</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>1.662</v>
+        <v>1.6</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I52" t="n">
-        <v>70.3</v>
+        <v>74.3</v>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>4/4 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+          <t>WWLWW (12 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>2-0</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4754,31 +6056,36 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>01:05</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+          <t>Rochester Americans vs Utica Comets</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>B. Van De Zandschulp</t>
+          <t>Utica Comets</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>1.55</v>
+        <v>2.25</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
@@ -4786,26 +6093,26 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>62.8</v>
+        <v>64.8</v>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLWD (7 pkt)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>82%</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4817,36 +6124,36 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>22:30</t>
+          <t>01:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>football</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1. Liga</t>
+          <t>AHL</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Lechia Gdansk vs Arka Gdynia</t>
+          <t>Grand Rapids Griffins vs Manitoba Moose</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lechia Gdansk</t>
+          <t>Grand Rapids Griffins</t>
         </is>
       </c>
       <c r="G54" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
@@ -4854,7 +6161,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>68.3</v>
+        <v>66.59999999999999</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
@@ -4863,17 +6170,17 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+          <t>WWWLW (12 pkt) vs DWWLW (10 pkt)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4885,36 +6192,36 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>22:45</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>CEX</t>
+          <t>League One</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Litvinov vs Karlovy Vary</t>
+          <t>Notts County vs Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Karlovy Vary</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G55" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
@@ -4922,7 +6229,7 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>65.3</v>
+        <v>60.4</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
@@ -4931,7 +6238,7 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+          <t>WDWWD (11 pkt) vs LWLWL (6 pkt)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4941,7 +6248,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4953,12 +6260,12 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -4968,21 +6275,21 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>SEW</t>
+          <t>FR1</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Engelholm W vs Linkopings W</t>
+          <t>Tours vs Tourcoing</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Engelholm W</t>
+          <t>Tours</t>
         </is>
       </c>
       <c r="G56" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
@@ -4990,7 +6297,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>72.7</v>
+        <v>75.7</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
@@ -4999,17 +6306,17 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+          <t>WLLWW (9 pkt) vs WLLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -5021,44 +6328,44 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>FR2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bojnice vs Voslauer</t>
+          <t>Hyeres-Toulon vs Le Havre</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bojnice</t>
+          <t>Hyeres-Toulon</t>
         </is>
       </c>
       <c r="G57" t="n">
-        <v>1.6</v>
+        <v>1.38</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>68.09999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
@@ -5067,17 +6374,17 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+          <t>LLWWW (9 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>4-0</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -5089,44 +6396,44 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>hockey</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>AHL</t>
+          <t>USC</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ritten vs Asiago</t>
+          <t>K. Miyoshi vs M. Cassone</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ritten</t>
+          <t>M. Cassone</t>
         </is>
       </c>
       <c r="G58" t="n">
-        <v>1.88</v>
+        <v>1.6</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>67.5</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
@@ -5135,17 +6442,17 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWLLW (6 pkt)</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -5157,36 +6464,36 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DE1</t>
+          <t>Liga 2</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Flensburg-H. vs Fuchse Berlin</t>
+          <t>ASA Târgu Mureș vs Chindia Targoviste</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Flensburg-H.</t>
+          <t>Chindia Targoviste</t>
         </is>
       </c>
       <c r="G59" t="n">
-        <v>1.7</v>
+        <v>2.1</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
@@ -5194,94 +6501,89 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>68.90000000000001</v>
+        <v>59.1</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+          <t>WWWWL (12 pkt) vs LWDWL (7 pkt)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>rugby</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>ERC</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Section Paloise vs Leicester Tigers</t>
+          <t>T. Samuel vs Z. Bergs</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Section Paloise</t>
+          <t>Z. Bergs</t>
         </is>
       </c>
       <c r="G60" t="n">
-        <v>1.63</v>
+        <v>1.38</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>75.3</v>
+        <v>63.3</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+          <t>LWWWL (9 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -5293,58 +6595,63 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>tennis</t>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>CEX</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>C. Burel vs L. Romero Gormaz</t>
+          <t>Karlovy Vary vs Kometa Brno</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>C. Burel</t>
+          <t>Karlovy Vary</t>
         </is>
       </c>
       <c r="G61" t="n">
-        <v>1.35</v>
+        <v>1.95</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>74.5</v>
+        <v>60.4</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>5/5 za</t>
+          <t>6/6 za</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+          <t>LWWLW (9 pkt) vs DWDDL (6 pkt)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -5356,44 +6663,44 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>04:35</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>rugby</t>
+          <t>hockey</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NPC</t>
+          <t>FI1</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Canterbury vs Taranaki</t>
+          <t>SaiPa vs Karpat</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Canterbury</t>
+          <t>SaiPa</t>
         </is>
       </c>
       <c r="G62" t="n">
-        <v>1.43</v>
+        <v>2</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>72.8</v>
+        <v>62.8</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
@@ -5402,17 +6709,17 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+          <t>WWLLW (9 pkt) vs DDDDD (5 pkt)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>3-2</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>65%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -5424,36 +6731,36 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>football</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>FR2</t>
+          <t>League 1</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ada Blois vs La Rochelle</t>
+          <t>Ario Eslamshahr vs Naft Bandar Abbas</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Ada Blois</t>
+          <t>Ario Eslamshahr</t>
         </is>
       </c>
       <c r="G63" t="n">
-        <v>1.38</v>
+        <v>2.5</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
@@ -5461,67 +6768,62 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>77.59999999999999</v>
+        <v>49.4</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>5/6 za</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+          <t>WLWWL (9 pkt) vs DLDWD (6 pkt)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>2-0</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PT2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Academica vs CB Queluz</t>
+          <t>J. Fearnley vs H. Gaston</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>CB Queluz</t>
+          <t>J. Fearnley</t>
         </is>
       </c>
       <c r="G64" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
@@ -5529,135 +6831,130 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>70.5</v>
+        <v>72.2</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+          <t>LWWWW (12 pkt) vs LWWLL (6 pkt)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>4-0</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>LNB</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Cholet vs Chalon/Saone</t>
+          <t>S. Kopp vs G. Cadenasso</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Cholet</t>
+          <t>G. Cadenasso</t>
         </is>
       </c>
       <c r="G65" t="n">
-        <v>1.68</v>
+        <v>1.45</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>71.7</v>
+        <v>84.2</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>6/6 za</t>
+          <t>4/5 za</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLLLL (0 pkt)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>5-0</t>
+          <t>0-0</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>⭐⭐⭐</t>
+          <t>⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>handball</t>
+          <t>basketball</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>CLW</t>
+          <t>CBA</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Odense W vs Gyor W</t>
+          <t>Beijing vs Guangdong</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Gyor W</t>
+          <t>Beijing</t>
         </is>
       </c>
       <c r="G66" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
@@ -5665,7 +6962,7 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>64.3</v>
+        <v>73.7</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
@@ -5674,17 +6971,17 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>85%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5696,104 +6993,94 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>PT2</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Santo Andre vs Maia</t>
+          <t>M. Donald vs C. Sanchez Jover</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Maia</t>
+          <t>M. Donald</t>
         </is>
       </c>
       <c r="G67" t="n">
-        <v>1.5</v>
+        <v>1.65</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="I67" t="n">
-        <v>65.59999999999999</v>
+        <v>83</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>5-0</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>DNW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>VCO Munster W vs Ostbevern W</t>
+          <t>R. M. Papoe vs O. Roca Batalla</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ostbevern W</t>
+          <t>R. M. Papoe</t>
         </is>
       </c>
       <c r="G68" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
@@ -5801,67 +7088,62 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>62.1</v>
+        <v>76.2</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>4/5 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLLWL (3 pkt)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>07:30</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>volleyball</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>PLW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Bydgoszcz W vs MKS Kalisz W</t>
+          <t>S. Kartal vs K. Birrell</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bydgoszcz W</t>
+          <t>S. Kartal</t>
         </is>
       </c>
       <c r="G69" t="n">
-        <v>1.53</v>
+        <v>1.4</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
@@ -5869,67 +7151,62 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>65.5</v>
+        <v>70.5</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+          <t>LWWWW (12 pkt) vs LLWWW (9 pkt)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-10-17</t>
+          <t>2026-10-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>04:40</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>basketball</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>AUW</t>
+          <t>tennis</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Perth Lynx W vs Townsville W</t>
+          <t>T. Valentova vs S. Zhang</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Townsville W</t>
+          <t>T. Valentova</t>
         </is>
       </c>
       <c r="G70" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
@@ -5937,104 +7214,1920 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>66.09999999999999</v>
+        <v>75.8</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>5/6 za</t>
+          <t>5/5 za</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+          <t>WLWWW (12 pkt) vs LLWLL (3 pkt)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>3-2</t>
+          <t>1-0</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>70%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>⭐⭐</t>
+          <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>04:15</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LBP</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Astros vs Mineros</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Astros</t>
+        </is>
+      </c>
+      <c r="G71" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>78.59999999999999</v>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NHL</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>New York Islanders vs Anaheim Ducks</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>New York Islanders</t>
+        </is>
+      </c>
+      <c r="G72" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I72" t="n">
+        <v>57.4</v>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>WDWLW (10 pkt) vs LLLWW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>01:00</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>NHL</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Washington Capitals vs Los Angeles Kings</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Washington Capitals</t>
+        </is>
+      </c>
+      <c r="G73" t="n">
+        <v>2</v>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I73" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>WWLLW (9 pkt) vs LLDLD (2 pkt)</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Primera C Metropolitana</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>CA Lugano vs Cañuelas FC</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Cañuelas FC</t>
+        </is>
+      </c>
+      <c r="G74" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I74" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs LLDDD (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>A. Hernandez vs F. Ribero</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>A. Hernandez</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>KZ1</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Karaganda vs Gornyak Rudny</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Karaganda</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I76" t="n">
+        <v>66.8</v>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>DWDWW (11 pkt) vs LDLWL (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>BLJ</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Utsunomiya Brex vs Gunma</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Gunma</t>
+        </is>
+      </c>
+      <c r="G77" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I77" t="n">
+        <v>59.3</v>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>LWLWW (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>12:05</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>BLJ</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Nagasaki vs Altiri Chiba</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Nagasaki</t>
+        </is>
+      </c>
+      <c r="G78" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I78" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>LLWWW (9 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>M. Cilic vs N. Basilashvili</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>N. Basilashvili</t>
+        </is>
+      </c>
+      <c r="G79" t="n">
+        <v>1.662</v>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I79" t="n">
+        <v>70.3</v>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>4/4 za</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LWLLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>B. Van De Zandschulp vs K. Majchrzak</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>B. Van De Zandschulp</t>
+        </is>
+      </c>
+      <c r="G80" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I80" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>LWWWL (9 pkt) vs LLWLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>1-0</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>22:30</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>football</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>1. Liga</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk vs Arka Gdynia</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Lechia Gdansk</t>
+        </is>
+      </c>
+      <c r="G81" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>68.3</v>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWLLD (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>78%</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>CEX</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Litvinov vs Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Karlovy Vary</t>
+        </is>
+      </c>
+      <c r="G82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I82" t="n">
+        <v>65.3</v>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLWDL (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>84%</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SEW</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Engelholm W vs Linkopings W</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Engelholm W</t>
+        </is>
+      </c>
+      <c r="G83" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I83" t="n">
+        <v>72.7</v>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>ECU</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Bojnice vs Voslauer</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Bojnice</t>
+        </is>
+      </c>
+      <c r="G84" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I84" t="n">
+        <v>68.09999999999999</v>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>WLWDW (10 pkt) vs LWLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>4-0</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>hockey</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AHL</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Ritten vs Asiago</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Ritten</t>
+        </is>
+      </c>
+      <c r="G85" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I85" t="n">
+        <v>67.5</v>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWDW (10 pkt)</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>DE1</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Flensburg-H. vs Fuchse Berlin</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Flensburg-H.</t>
+        </is>
+      </c>
+      <c r="G86" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>68.90000000000001</v>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WLWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>ERC</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Section Paloise vs Leicester Tigers</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Section Paloise</t>
+        </is>
+      </c>
+      <c r="G87" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="I87" t="n">
+        <v>75.3</v>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>WWWLW (12 pkt) vs WWLLL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>tennis</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>C. Burel vs L. Romero Gormaz</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>C. Burel</t>
+        </is>
+      </c>
+      <c r="G88" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I88" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>5/5 za</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs WWWWL (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>04:35</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>rugby</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NPC</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Canterbury vs Taranaki</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Canterbury</t>
+        </is>
+      </c>
+      <c r="G89" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I89" t="n">
+        <v>72.8</v>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>WWWWW (15 pkt) vs LWWWW (12 pkt)</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>20:00</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>FR2</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Ada Blois vs La Rochelle</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Ada Blois</t>
+        </is>
+      </c>
+      <c r="G90" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I90" t="n">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>2-0</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Academica vs CB Queluz</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>CB Queluz</t>
+        </is>
+      </c>
+      <c r="G91" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I91" t="n">
+        <v>70.5</v>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>WWLWW (12 pkt) vs LLLLL (0 pkt)</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LNB</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Cholet vs Chalon/Saone</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Cholet</t>
+        </is>
+      </c>
+      <c r="G92" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I92" t="n">
+        <v>71.7</v>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>WWWWL (12 pkt) vs LWWLW (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>5-0</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>handball</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CLW</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Odense W vs Gyor W</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gyor W</t>
+        </is>
+      </c>
+      <c r="G93" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>6/6 za</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>WDWWW (13 pkt) vs WWWLL (9 pkt)</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>⭐⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>PT2</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Santo Andre vs Maia</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Maia</t>
+        </is>
+      </c>
+      <c r="G94" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I94" t="n">
+        <v>65.59999999999999</v>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>WLWWW (12 pkt) vs WLLLW (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>DNW</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>VCO Munster W vs Ostbevern W</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Ostbevern W</t>
+        </is>
+      </c>
+      <c r="G95" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I95" t="n">
+        <v>62.1</v>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>4/5 za</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>LLLWW (6 pkt) vs LLWLL (3 pkt)</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2-2</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>brak</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>volleyball</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>PLW</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W vs MKS Kalisz W</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Bydgoszcz W</t>
+        </is>
+      </c>
+      <c r="G96" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I96" t="n">
+        <v>65.5</v>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>WLWWL (9 pkt) vs LLWWL (6 pkt)</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>4-1</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>AUW</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Perth Lynx W vs Townsville W</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Townsville W</t>
+        </is>
+      </c>
+      <c r="G97" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="I97" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>5/6 za</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>WDWWL (10 pkt) vs LLDLW (4 pkt)</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>3-2</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>⭐⭐</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2026-10-17</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
         <is>
           <t>07:00</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>football</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D98" t="inlineStr">
         <is>
           <t>J1 League</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E98" t="inlineStr">
         <is>
           <t>JEF United Chiba vs Yokohama Marinos</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F98" t="inlineStr">
         <is>
           <t>Yokohama Marinos</t>
         </is>
       </c>
-      <c r="G71" t="n">
+      <c r="G98" t="n">
         <v>2</v>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="I71" t="n">
+      <c r="I98" t="n">
         <v>56.3</v>
       </c>
-      <c r="J71" t="inlineStr">
+      <c r="J98" t="inlineStr">
         <is>
           <t>6/6 za</t>
         </is>
       </c>
-      <c r="K71" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>WDWWW (13 pkt) vs DLLLD (2 pkt)</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr">
+      <c r="L98" t="inlineStr">
         <is>
           <t>2-1</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr">
+      <c r="M98" t="inlineStr">
         <is>
           <t>76%</t>
         </is>
       </c>
-      <c r="N71" t="inlineStr">
+      <c r="N98" t="inlineStr">
         <is>
           <t>⭐⭐⭐</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O71"/>
+  <autoFilter ref="A1:O98"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$208</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,794 +523,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>10:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>baseball</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>NPB</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Fukuoka S. Hawks vs Yokohama BayStars</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Fukuoka S. Hawks</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>1.488</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>68.7</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>WWWWW (15 pkt) vs LLWWW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>WWWWW / LLWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Liga Revelacao U23</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Farense U23 vs Academico Viseu U23</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Academico Viseu U23</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>53.7</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>3/4 za</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs LLLWW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>1st Division</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Al Ta'i vs Jeddah Club</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Al Ta'i</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>53</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>3/4 za</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>LLWLW (6 pkt) vs LLLLW (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CH1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Lausanne vs Langnau Tigers</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Lausanne</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>74.2</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>WLLWL (6 pkt) vs DLWLL (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>4.0-0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>WLLWL / DLWLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CH1</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Ambri-Piotta vs Biel</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Ambri-Piotta</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>65.09999999999999</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WLWWL (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>3.0-1.5</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>WLWWW / WLWWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>N. Jarry vs H. Dellien</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>H. Dellien</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3/4 za</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>LLWWW (9 pkt) vs LWLWL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Morzine-Avoriaz vs Caen</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Caen</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>62.8</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>WWDDD (9 pkt) vs LLLLW (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>3.0-2.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>73%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>WWDD / LLLLW</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>FR2</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Valence vs Villard</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Villard</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>61.2</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>WLWWL (9 pkt) vs DWDLL (5 pkt)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>0.5-0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>WLWWL / DWDLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>AFC Champions League 2</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Shorta Baghdad vs Hussein Irbid</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Shorta Baghdad</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>54.6</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>WDWDW (11 pkt) vs WLWWD (10 pkt)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>3.0-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>WDWDW / WLWWD</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Serie B</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Ascoli vs Sampdoria</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Ascoli</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>58.1</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>WDDWL (8 pkt) vs DLLWL (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>WDDWL / DLLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>SPL Premier Division</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Plymouth Parkway vs Gloucester</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Plymouth Parkway</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>49.4</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4/6 za</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>LWWLW (9 pkt) vs DLDWW (8 pkt)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>1.0-1.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>LWWLW / LDWW</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O12"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/results/TOP.xlsx
+++ b/results/TOP.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wszystkie" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Do gry'!$A$1:$O$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Wszystkie'!$A$1:$O$265</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O41"/>
+  <dimension ref="A1:O1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -523,2886 +523,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Liga Profesional</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>CA Huracán vs CA Tigre</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>CA Huracán</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>54.3</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>LLLWW (6 pkt) vs LDLLL (1 pkt)</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>1.0-0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>LLLWW / LDLLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>NHL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Florida Panthers vs Winnipeg Jets</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Florida Panthers</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>65.90000000000001</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>WWLLW (9 pkt) vs LLLDL (1 pkt)</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>2.5-1.5</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>WWLLW / LLLDL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>00:05</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>AHL</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Rochester Americans vs Lehigh Valley Phantoms</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Lehigh Valley Phantoms</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>WLDWW (10 pkt) vs LDLLW (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2.5-0.5</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>WLDWW / LDLLW</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>03:00</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NHL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Anaheim Ducks vs Buffalo Sabres</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Buffalo Sabres</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>WWDLD (8 pkt) vs LDWLL (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>3.0-1.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>WWDLD / LDWLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>A. Eala vs D. Shnaider</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>D. Shnaider</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>63.9</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WWLWL (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>68%</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>12:25</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Liga Alef North</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Hapoel Beit Shean vs FC Tira</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>FC Tira</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>57.4</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>LWWWW (12 pkt) vs LWDDW (8 pkt)</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>1.5-0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>LWWWW / LWDDW</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>12:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>RU4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Krasnoyarskie Rysi vs Sputnik Almetievsk</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Krasnoyarskie Rysi</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>1.541</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>WWWLL (9 pkt) vs LLLLL (0 pkt)</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>13:00</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>V-League</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bac Ninh vs Hoang Anh Gia Lai</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bac Ninh</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>53.6</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>3/4 za</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>13:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Liga Alef North</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Hapoel Bnei Musmus vs Hapoel Migdal HaEmek</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Hapoel Migdal HaEmek</t>
-        </is>
-      </c>
-      <c r="G10" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>71.90000000000001</v>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>WWDWD (11 pkt) vs LLLDW (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>1.5-0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>WWDWD / LLLDW</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kowloon City vs HK Rangers</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Kowloon City</t>
-        </is>
-      </c>
-      <c r="G11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>DDLWW (8 pkt) vs LLLLW (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>2.5-1.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>DLWW / LLLLW</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>14:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>KZ1</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Torpedo vs Nomad Astana</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Torpedo</t>
-        </is>
-      </c>
-      <c r="G12" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>66.3</v>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>WWWWW (15 pkt) vs LLWWW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>3.0-2.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>92%</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>WWWWW / LLWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Liga 3 Seria 3</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>Urban Titu vs Metalul Plopeni</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Urban Titu</t>
-        </is>
-      </c>
-      <c r="G13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>61.3</v>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>LWWDD (8 pkt) vs LLLDW (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>LWWDD / LLLDW</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>KZ1</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Gornyak Rudny vs Kokshetau</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Kokshetau</t>
-        </is>
-      </c>
-      <c r="G14" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>72.7</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>WWWWW (15 pkt) vs LWLLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>WWWWW / LWLLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>Turan Tovuz vs Sabah</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Sabah</t>
-        </is>
-      </c>
-      <c r="G15" t="n">
-        <v>2</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>59.2</v>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>5/6 za</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>DLWWD (8 pkt) vs DLWLW (7 pkt)</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>3.0-0.5</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>DLWWD / DLWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>RU4</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>AKM-Junior vs Belye Medvedi</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Belye Medvedi</t>
-        </is>
-      </c>
-      <c r="G16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>60.7</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>WWLWW (12 pkt) vs LLLWW (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Division 1</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>Al Hashemeya vs Yarmouk Amman</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Yarmouk Amman</t>
-        </is>
-      </c>
-      <c r="G17" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>47.6</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>3/4 za</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WLWLW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>58%</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>FIU</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>IFK Helsinki U20 vs Jokerit U20</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>IFK Helsinki U20</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>69.90000000000001</v>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>LDWWL (7 pkt) vs LDLLL (1 pkt)</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>LDWWL / LDLLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>CEX</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>Plzen vs Trinec</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Trinec</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I19" t="n">
-        <v>62.6</v>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>DWLWW (10 pkt) vs DLLDL (2 pkt)</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>DWLWW / DLLDL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>17:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>FI1</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>SaiPa vs JYP</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>SaiPa</t>
-        </is>
-      </c>
-      <c r="G20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>57.8</v>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>LWWDW (10 pkt) vs LWWDD (8 pkt)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>3.0-2.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>LWWDW / LWWDD</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>SK1</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Liptovsky Mikulas vs Spisska Nova Ves</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Liptovsky Mikulas</t>
-        </is>
-      </c>
-      <c r="G21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I21" t="n">
-        <v>58.6</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>DWLWL (7 pkt) vs DLLWL (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>3.0-2.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>DWLWL / DLLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>CEX</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Olomouc vs Ceske Budejovice</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Ceske Budejovice</t>
-        </is>
-      </c>
-      <c r="G22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>57.7</v>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>WDWLW (10 pkt) vs DDWLL (5 pkt)</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>WDWLW / DDWLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>tennis</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>J. Aguilar Cardozo vs L. Midon</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>L. Midon</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I23" t="n">
-        <v>69.40000000000001</v>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>WWLWW (12 pkt) vs WWLLW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>1.5-0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>63%</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>FIU</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>Kiekko-Espoo U20 vs Karpat U20</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Kiekko-Espoo U20</t>
-        </is>
-      </c>
-      <c r="G24" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I24" t="n">
-        <v>63.8</v>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>WWDWL (10 pkt) vs LLWWW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>2.0-0.5</t>
-        </is>
-      </c>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>80%</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>WWDWL / LLWWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>FI1</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>KalPa vs Jokerit</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>KalPa</t>
-        </is>
-      </c>
-      <c r="G25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I25" t="n">
-        <v>58.2</v>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>4/5 za</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>WWLWL (9 pkt) vs WDLLD (5 pkt)</t>
-        </is>
-      </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>WWLWL / WDLLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>SES</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Karlskrona vs Boras</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Karlskrona</t>
-        </is>
-      </c>
-      <c r="G26" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I26" t="n">
-        <v>70.09999999999999</v>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>WWDWD (11 pkt) vs DWLWW (10 pkt)</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>WWDWD / DWLWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>SE2</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Vasteras vs Kalmar</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="G27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>WLWLD (7 pkt) vs DDWDL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>4.5-0</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>WLWLD / DDWDL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>SE2</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Oskarshamn vs Ostersund</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Oskarshamn</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I28" t="n">
-        <v>67.40000000000001</v>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>WLDWW (10 pkt) vs LDDWL (5 pkt)</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>2.5-1.5</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>WLDWW / LDDWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>19:00</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>DE1</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Bietigheim-Metterzimmern vs Erlangen</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Erlangen</t>
-        </is>
-      </c>
-      <c r="G29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I29" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>LWWLW (9 pkt) vs LLWLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>0.5-0</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>LWWLW / LLWLL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>DE1</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Nurnberg Ice Tigers vs Grizzly Wolfsburg</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Nurnberg Ice Tigers</t>
-        </is>
-      </c>
-      <c r="G30" t="n">
-        <v>2</v>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I30" t="n">
-        <v>69.8</v>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>WWWLL (9 pkt) vs DLLLD (2 pkt)</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>3.0-1.5</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>WWWLL / DLLLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>DE1</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Krefeld Pinguine vs Kolner</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Kolner</t>
-        </is>
-      </c>
-      <c r="G31" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I31" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>5/5 za</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>DWDWL (8 pkt) vs WLLLD (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>DWDWL / WLLLD</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>19:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>DE1</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Adler Mannheim vs Bremerhaven</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Adler Mannheim</t>
-        </is>
-      </c>
-      <c r="G32" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I32" t="n">
-        <v>71.59999999999999</v>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>DWLWL (7 pkt) vs WLLWL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>DWLWL / WLLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>19:45</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>CH1</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Zug vs Langnau Tigers</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Zug</t>
-        </is>
-      </c>
-      <c r="G33" t="n">
-        <v>1.654</v>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I33" t="n">
-        <v>61</v>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WWLLW (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr"/>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Premier League</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Ittihad Alexandria vs Tala'ea Al Jaish</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Ittihad Alexandria</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I34" t="n">
-        <v>58.5</v>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>4/4 za</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>LWLWW (9 pkt) vs LLLLW (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr"/>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>20:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>handball</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>FRW</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Achenheim Truchtersheim W vs Besancon W</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Besancon W</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I35" t="n">
-        <v>61.5</v>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>WLWWW (12 pkt) vs WLDWW (10 pkt)</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>1.5-1.0</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>76%</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>WLWWW / WLDWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>20:15</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Amiens vs Briancon</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Amiens</t>
-        </is>
-      </c>
-      <c r="G36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I36" t="n">
-        <v>70.5</v>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>DWLWW (10 pkt) vs WLLWL (6 pkt)</t>
-        </is>
-      </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>3.5-1.0</t>
-        </is>
-      </c>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>DWLWW / WLLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>20:30</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>FR1</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Anglet vs Cergy-Pontoise</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Cergy-Pontoise</t>
-        </is>
-      </c>
-      <c r="G37" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I37" t="n">
-        <v>67</v>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>LWWWD (10 pkt) vs LDLWW (7 pkt)</t>
-        </is>
-      </c>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>LWWWD / LDLWW</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>SV Elversberg vs Mainz</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="G38" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I38" t="n">
-        <v>50.1</v>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>4/5 za</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>LLWLW (6 pkt) vs LLWLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>LLWL / LLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>21:45</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>football</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Premier</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Airbus UK vs Caernarfon Town</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Caernarfon Town</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>4/5 za</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>WWWLD (10 pkt) vs WLWWL (9 pkt)</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>brak</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>⭐⭐</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>WWWLD / WLWWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>NCAA</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Miami vs St. Thomas Tommies</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Miami</t>
-        </is>
-      </c>
-      <c r="G40" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>78</v>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>DWWWW (13 pkt) vs LLWLL (3 pkt)</t>
-        </is>
-      </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>5.0-0</t>
-        </is>
-      </c>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>89%</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>DWWWW / LLWL</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>2026-10-30</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>22:00</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>hockey</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>NCAA</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Holy Cross Crusaders vs Bentley Falcons</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bentley Falcons</t>
-        </is>
-      </c>
-      <c r="G41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>6/6 za</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>WWLLL (6 pkt) vs LWLLD (4 pkt)</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>4.0-1.0</t>
-        </is>
-      </c>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>86%</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>⭐⭐⭐</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>WWLLL / LWLLD</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:O41"/>
+  <autoFilter ref="A1:O1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
